--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -5,24 +5,24 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E11FA33-5372-4A0B-B953-CCB384A34663}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE33E97-AA7F-438E-8788-4027996D7BCB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
-    <sheet name="03-02-2026" sheetId="29" r:id="rId2"/>
+    <sheet name="03-02-20261" sheetId="33" r:id="rId2"/>
     <sheet name="03-03-2026" sheetId="30" r:id="rId3"/>
     <sheet name="03-04-2026" sheetId="31" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03-03-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'03-04-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,12 +369,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="64">
@@ -1227,7 +1233,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1508,10 +1514,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1526,19 +1529,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1552,6 +1549,27 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1873,7 +1891,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BB81"/>
+  <dimension ref="A1:BB83"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
@@ -1908,21 +1926,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1934,17 +1952,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="95"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="101"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -1964,13 +1982,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="105" t="s">
+      <c r="T4" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="107" t="s">
+      <c r="U4" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2010,10 +2028,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2021,9 +2039,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -3791,11 +3809,11 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="53"/>
       <c r="R39" s="81"/>
       <c r="S39" s="56"/>
       <c r="T39" s="84"/>
@@ -4505,280 +4523,324 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="30" t="s">
+    <row r="59" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="111"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
+      <c r="H59" s="112"/>
+      <c r="I59" s="112"/>
+      <c r="J59" s="112"/>
+      <c r="K59" s="112"/>
+      <c r="M59" s="112"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="112"/>
+      <c r="P59" s="112"/>
+      <c r="Q59" s="112"/>
+      <c r="R59" s="112"/>
+      <c r="S59" s="56"/>
+      <c r="T59" s="112"/>
+      <c r="U59" s="112"/>
+      <c r="V59" s="112"/>
+    </row>
+    <row r="60" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="111"/>
+      <c r="C60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="112"/>
+      <c r="M60" s="112"/>
+      <c r="N60" s="112"/>
+      <c r="O60" s="112"/>
+      <c r="P60" s="112"/>
+      <c r="Q60" s="112"/>
+      <c r="R60" s="112"/>
+      <c r="S60" s="56"/>
+      <c r="T60" s="112"/>
+      <c r="U60" s="112"/>
+      <c r="V60" s="112"/>
+    </row>
+    <row r="61" spans="1:22" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C62" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
-      <c r="U60" s="24" t="s">
+      <c r="D62" s="96"/>
+      <c r="E62" s="96"/>
+      <c r="F62" s="96"/>
+      <c r="G62" s="96"/>
+      <c r="H62" s="96"/>
+      <c r="I62" s="96"/>
+      <c r="J62" s="96"/>
+      <c r="K62" s="97"/>
+      <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B61" s="31" t="s">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B63" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="20"/>
-      <c r="U61" s="7"/>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B62" s="32" t="s">
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="20"/>
+      <c r="U63" s="7"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="44"/>
-      <c r="K62" s="21"/>
-      <c r="U62" s="3"/>
-    </row>
-    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="33" t="s">
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="44"/>
+      <c r="K64" s="21"/>
+      <c r="U64" s="3"/>
+    </row>
+    <row r="65" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="46"/>
-      <c r="K63" s="23"/>
-      <c r="U63" s="8"/>
-    </row>
-    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B65" s="31" t="s">
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="46"/>
+      <c r="K65" s="23"/>
+      <c r="U65" s="8"/>
+    </row>
+    <row r="66" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B67" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="20"/>
-      <c r="U65" s="7"/>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B66" s="32" t="s">
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="45"/>
+      <c r="K67" s="20"/>
+      <c r="U67" s="7"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B68" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="21"/>
-      <c r="U66" s="3"/>
-    </row>
-    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="33" t="s">
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="44"/>
+      <c r="K68" s="21"/>
+      <c r="U68" s="3"/>
+    </row>
+    <row r="69" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="23"/>
-      <c r="U67" s="8"/>
-    </row>
-    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B69" s="31" t="s">
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="46"/>
+      <c r="K69" s="23"/>
+      <c r="U69" s="8"/>
+    </row>
+    <row r="70" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B71" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="45"/>
-      <c r="K69" s="20"/>
-      <c r="U69" s="7"/>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B70" s="32" t="s">
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="20"/>
+      <c r="U71" s="7"/>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B72" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="21"/>
-      <c r="U70" s="3"/>
-    </row>
-    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="33" t="s">
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="21"/>
+      <c r="U72" s="3"/>
+    </row>
+    <row r="73" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="23"/>
-      <c r="U71" s="8"/>
-    </row>
-    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B73" s="31" t="s">
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="46"/>
+      <c r="K73" s="23"/>
+      <c r="U73" s="8"/>
+    </row>
+    <row r="74" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B75" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="45"/>
-      <c r="K73" s="20"/>
-      <c r="U73" s="7"/>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B74" s="32" t="s">
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="20"/>
+      <c r="U75" s="7"/>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B76" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="44"/>
-      <c r="K74" s="21"/>
-      <c r="U74" s="3"/>
-    </row>
-    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="33" t="s">
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="44"/>
+      <c r="K76" s="21"/>
+      <c r="U76" s="3"/>
+    </row>
+    <row r="77" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="23"/>
-      <c r="U75" s="8"/>
-    </row>
-    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B77" s="31" t="s">
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="46"/>
+      <c r="K77" s="23"/>
+      <c r="U77" s="8"/>
+    </row>
+    <row r="78" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B79" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="45"/>
-      <c r="K77" s="20"/>
-      <c r="U77" s="7"/>
-    </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B78" s="32" t="s">
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="20"/>
+      <c r="U79" s="7"/>
+    </row>
+    <row r="80" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B80" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="44"/>
-      <c r="K78" s="21"/>
-      <c r="U78" s="3"/>
-    </row>
-    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="33" t="s">
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="44"/>
+      <c r="K80" s="21"/>
+      <c r="U80" s="3"/>
+    </row>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C79" s="22"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="22"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="23"/>
-      <c r="U79" s="8"/>
-    </row>
-    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="30" t="s">
+      <c r="C81" s="22"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="46"/>
+      <c r="K81" s="23"/>
+      <c r="U81" s="8"/>
+    </row>
+    <row r="82" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="47"/>
-      <c r="K81" s="18"/>
-      <c r="U81" s="16"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="17"/>
+      <c r="J83" s="47"/>
+      <c r="K83" s="18"/>
+      <c r="U83" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C62:K62"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4790,7 +4852,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EACB38A-97B0-45C8-A623-33FB2F149B95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCB6E3F5-60FD-438D-9CA9-F1C4B96DB6D9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4829,21 +4891,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4855,17 +4917,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="95"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="101"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4885,13 +4947,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="105" t="s">
+      <c r="T4" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="107" t="s">
+      <c r="U4" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -4931,20 +4993,20 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4978,13 +5040,13 @@
       <c r="G6" s="40"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
-      <c r="J6" s="52"/>
+      <c r="J6" s="94"/>
       <c r="K6" s="38"/>
       <c r="M6" s="37"/>
       <c r="N6" s="49"/>
       <c r="O6" s="40"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
       <c r="R6" s="38"/>
       <c r="S6" s="9"/>
       <c r="T6" s="39"/>
@@ -5021,34 +5083,51 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <f>21+41</f>
+        <v>62</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>2</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1629</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>67.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -5083,7 +5162,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>15+62+25</f>
+        <v>102</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -5106,11 +5188,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -5145,7 +5227,10 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <f>5+71</f>
+        <v>76</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -5155,11 +5240,17 @@
       <c r="J9" s="72"/>
       <c r="K9" s="73"/>
       <c r="L9" s="56"/>
-      <c r="M9" s="74"/>
+      <c r="M9" s="74">
+        <v>1</v>
+      </c>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>2</v>
+      </c>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>1</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -5168,11 +5259,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -5207,7 +5298,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>38</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -5217,9 +5310,13 @@
       <c r="J10" s="72"/>
       <c r="K10" s="73"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="74"/>
+      <c r="M10" s="74">
+        <v>1</v>
+      </c>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
       <c r="R10" s="73"/>
@@ -5230,11 +5327,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -5269,15 +5366,21 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -5288,15 +5391,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -5329,7 +5432,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>576+72+1+720+63+60+1008+36+1440</f>
+        <v>3976</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -5339,24 +5445,34 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
+      <c r="M12" s="64">
+        <v>11</v>
+      </c>
+      <c r="N12" s="65">
+        <v>23</v>
+      </c>
+      <c r="O12" s="66">
+        <v>14</v>
+      </c>
       <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="Q12" s="67">
+        <v>20</v>
+      </c>
+      <c r="R12" s="68">
+        <v>20</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>96547</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>4022.7916666666665</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -5398,7 +5514,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -5421,11 +5539,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -5642,7 +5760,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -5665,11 +5785,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -5763,7 +5883,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -5786,11 +5908,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -5824,7 +5946,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -5847,11 +5971,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -5885,7 +6009,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -5908,11 +6034,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -5946,7 +6072,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -5969,11 +6097,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -6016,7 +6144,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>42</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -6026,11 +6156,17 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>2</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="71">
+        <v>1</v>
+      </c>
       <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="Q23" s="72">
+        <v>2</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
@@ -6039,11 +6175,11 @@
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -6086,7 +6222,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -6109,11 +6247,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -6147,17 +6285,26 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>63+59+1</f>
+        <v>123</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>2</v>
+      </c>
       <c r="N25" s="75"/>
       <c r="O25" s="71"/>
       <c r="P25" s="72"/>
@@ -6166,15 +6313,15 @@
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3011</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>125.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -6189,7 +6336,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>20</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -6212,11 +6361,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -6274,7 +6423,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+32</f>
+        <v>96</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -6284,11 +6436,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>3</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -6297,11 +6455,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2472</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -6321,7 +6479,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>10</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -6344,11 +6504,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -6359,7 +6519,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>57</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -6371,9 +6533,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -6382,11 +6548,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -6397,7 +6563,10 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="71"/>
+      <c r="C31" s="71">
+        <f>11+4</f>
+        <v>15</v>
+      </c>
       <c r="D31" s="71"/>
       <c r="E31" s="71"/>
       <c r="F31" s="71"/>
@@ -6409,7 +6578,9 @@
       <c r="L31" s="56"/>
       <c r="M31" s="74"/>
       <c r="N31" s="75"/>
-      <c r="O31" s="71"/>
+      <c r="O31" s="71">
+        <v>1</v>
+      </c>
       <c r="P31" s="72"/>
       <c r="Q31" s="72"/>
       <c r="R31" s="73"/>
@@ -6420,11 +6591,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -6473,7 +6644,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="71"/>
+      <c r="C33" s="71">
+        <v>3</v>
+      </c>
       <c r="D33" s="71"/>
       <c r="E33" s="71"/>
       <c r="F33" s="71"/>
@@ -6496,11 +6669,11 @@
       </c>
       <c r="U33" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V33" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -6511,34 +6684,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>70+72</f>
+        <v>142</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
+      <c r="N34" s="75">
+        <v>12</v>
+      </c>
       <c r="O34" s="71"/>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3497</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>145.70833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6625,34 +6811,47 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>540+51+2376+1512</f>
+        <v>4479</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>35</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>42</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>79</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>27818</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4636.333333333333</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -6664,7 +6863,10 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <f>15+2+2</f>
+        <v>19</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -6687,11 +6889,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -6712,11 +6914,11 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="53"/>
       <c r="R39" s="81"/>
       <c r="S39" s="56"/>
       <c r="T39" s="84"/>
@@ -6731,34 +6933,45 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>51+504</f>
+        <v>555</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>13416</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>559</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6769,7 +6982,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1440+6</f>
+        <v>1446</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
@@ -6779,11 +6995,17 @@
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>10</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>9</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>20</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
@@ -6792,11 +7014,11 @@
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>17820</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6836,34 +7058,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>864+84+5940+8424+5400+4644+7128</f>
+        <v>32484</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="66">
+        <v>1</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>4*6+3</f>
+        <v>27</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>419</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>364</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>425</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>202750</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>33791.666666666664</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6941,7 +7182,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="71"/>
+      <c r="C46" s="71">
+        <v>4</v>
+      </c>
       <c r="D46" s="71"/>
       <c r="E46" s="71"/>
       <c r="F46" s="71"/>
@@ -6964,11 +7207,11 @@
       </c>
       <c r="U46" s="76">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="76">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6979,7 +7222,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>22+2268+44</f>
+        <v>2334</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -6987,26 +7233,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>7</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14134</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2355.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -7017,7 +7273,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -7040,11 +7298,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -7131,7 +7389,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -7154,11 +7414,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -7207,7 +7467,10 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <f>4+2</f>
+        <v>6</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -7230,11 +7493,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -7360,7 +7623,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>46165</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -7374,56 +7637,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>756</v>
+      </c>
+      <c r="U58" s="110">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>394098</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>47776.499999999993</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7431,17 +7694,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="96"/>
+      <c r="E60" s="96"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="96"/>
+      <c r="H60" s="96"/>
+      <c r="I60" s="96"/>
+      <c r="J60" s="96"/>
+      <c r="K60" s="97"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -7693,13 +7956,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -7750,21 +8013,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -7776,17 +8039,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="95"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="101"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -7806,13 +8069,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="105" t="s">
+      <c r="T4" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="107" t="s">
+      <c r="U4" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -7852,10 +8115,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -7863,9 +8126,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10352,17 +10615,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="96"/>
+      <c r="E60" s="96"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="96"/>
+      <c r="H60" s="96"/>
+      <c r="I60" s="96"/>
+      <c r="J60" s="96"/>
+      <c r="K60" s="97"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -10671,21 +10934,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -10697,17 +10960,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="95"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="101"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -10727,13 +10990,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="105" t="s">
+      <c r="T4" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="107" t="s">
+      <c r="U4" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -10773,10 +11036,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -10784,9 +11047,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="105"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13273,17 +13536,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="96" t="s">
+      <c r="C60" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="97"/>
-      <c r="G60" s="97"/>
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
-      <c r="J60" s="97"/>
-      <c r="K60" s="98"/>
+      <c r="D60" s="96"/>
+      <c r="E60" s="96"/>
+      <c r="F60" s="96"/>
+      <c r="G60" s="96"/>
+      <c r="H60" s="96"/>
+      <c r="I60" s="96"/>
+      <c r="J60" s="96"/>
+      <c r="K60" s="97"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE33E97-AA7F-438E-8788-4027996D7BCB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F91FC4-71A8-473F-95F3-0B0D421BB222}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
     <sheet name="03-02-20261" sheetId="33" r:id="rId2"/>
-    <sheet name="03-03-2026" sheetId="30" r:id="rId3"/>
-    <sheet name="03-04-2026" sheetId="31" r:id="rId4"/>
+    <sheet name="03-04-2026" sheetId="30" r:id="rId3"/>
+    <sheet name="03-06-2026" sheetId="31" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'03-03-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'03-04-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03-04-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'03-06-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="73">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>DATE: 03/02/2026</t>
-  </si>
-  <si>
-    <t>DATE: 03/03/2026</t>
   </si>
   <si>
     <t>DATE: 03/04/2026</t>
@@ -1517,6 +1514,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1549,27 +1567,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1926,21 +1923,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="98" t="s">
+      <c r="I1" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1952,17 +1949,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="C4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="101"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -1982,13 +1979,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="102" t="s">
+      <c r="T4" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="104" t="s">
+      <c r="U4" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="98" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2028,10 +2025,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="101"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2039,9 +2036,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="99"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4524,65 +4521,65 @@
       </c>
     </row>
     <row r="59" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="111"/>
-      <c r="C59" s="112"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="112"/>
-      <c r="H59" s="112"/>
-      <c r="I59" s="112"/>
-      <c r="J59" s="112"/>
-      <c r="K59" s="112"/>
-      <c r="M59" s="112"/>
-      <c r="N59" s="112"/>
-      <c r="O59" s="112"/>
-      <c r="P59" s="112"/>
-      <c r="Q59" s="112"/>
-      <c r="R59" s="112"/>
+      <c r="B59" s="96"/>
+      <c r="C59" s="97"/>
+      <c r="D59" s="97"/>
+      <c r="E59" s="97"/>
+      <c r="F59" s="97"/>
+      <c r="G59" s="97"/>
+      <c r="H59" s="97"/>
+      <c r="I59" s="97"/>
+      <c r="J59" s="97"/>
+      <c r="K59" s="97"/>
+      <c r="M59" s="97"/>
+      <c r="N59" s="97"/>
+      <c r="O59" s="97"/>
+      <c r="P59" s="97"/>
+      <c r="Q59" s="97"/>
+      <c r="R59" s="97"/>
       <c r="S59" s="56"/>
-      <c r="T59" s="112"/>
-      <c r="U59" s="112"/>
-      <c r="V59" s="112"/>
+      <c r="T59" s="97"/>
+      <c r="U59" s="97"/>
+      <c r="V59" s="97"/>
     </row>
     <row r="60" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="111"/>
-      <c r="C60" s="112"/>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="112"/>
-      <c r="M60" s="112"/>
-      <c r="N60" s="112"/>
-      <c r="O60" s="112"/>
-      <c r="P60" s="112"/>
-      <c r="Q60" s="112"/>
-      <c r="R60" s="112"/>
+      <c r="B60" s="96"/>
+      <c r="C60" s="97"/>
+      <c r="D60" s="97"/>
+      <c r="E60" s="97"/>
+      <c r="F60" s="97"/>
+      <c r="G60" s="97"/>
+      <c r="H60" s="97"/>
+      <c r="I60" s="97"/>
+      <c r="J60" s="97"/>
+      <c r="K60" s="97"/>
+      <c r="M60" s="97"/>
+      <c r="N60" s="97"/>
+      <c r="O60" s="97"/>
+      <c r="P60" s="97"/>
+      <c r="Q60" s="97"/>
+      <c r="R60" s="97"/>
       <c r="S60" s="56"/>
-      <c r="T60" s="112"/>
-      <c r="U60" s="112"/>
-      <c r="V60" s="112"/>
+      <c r="T60" s="97"/>
+      <c r="U60" s="97"/>
+      <c r="V60" s="97"/>
     </row>
     <row r="61" spans="1:22" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="95" t="s">
+      <c r="C62" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="96"/>
-      <c r="E62" s="96"/>
-      <c r="F62" s="96"/>
-      <c r="G62" s="96"/>
-      <c r="H62" s="96"/>
-      <c r="I62" s="96"/>
-      <c r="J62" s="96"/>
-      <c r="K62" s="97"/>
+      <c r="D62" s="103"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="103"/>
+      <c r="G62" s="103"/>
+      <c r="H62" s="103"/>
+      <c r="I62" s="103"/>
+      <c r="J62" s="103"/>
+      <c r="K62" s="104"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4891,21 +4888,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="98" t="s">
+      <c r="I1" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4917,17 +4914,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="C4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="101"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4947,13 +4944,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="102" t="s">
+      <c r="T4" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="104" t="s">
+      <c r="U4" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="98" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -4993,10 +4990,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="101"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5004,9 +5001,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="99"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7680,7 +7677,7 @@
         <f>SUM(T7:T57)</f>
         <v>756</v>
       </c>
-      <c r="U58" s="110">
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
         <v>394098</v>
       </c>
@@ -7694,17 +7691,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="95" t="s">
+      <c r="C60" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="96"/>
-      <c r="E60" s="96"/>
-      <c r="F60" s="96"/>
-      <c r="G60" s="96"/>
-      <c r="H60" s="96"/>
-      <c r="I60" s="96"/>
-      <c r="J60" s="96"/>
-      <c r="K60" s="97"/>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="104"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -7956,13 +7953,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -8013,21 +8010,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="98" t="s">
+      <c r="I1" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8039,17 +8036,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="C4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="101"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8069,13 +8066,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="102" t="s">
+      <c r="T4" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="104" t="s">
+      <c r="U4" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="98" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8115,10 +8112,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="101"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8126,9 +8123,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="99"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -8205,34 +8202,51 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <f>21+41</f>
+        <v>62</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>66.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -8267,7 +8281,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>62+23+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -8281,7 +8298,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -8290,11 +8309,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -8329,7 +8348,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>66</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -8341,9 +8362,13 @@
       <c r="L9" s="56"/>
       <c r="M9" s="74"/>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>2</v>
+      </c>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>8</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -8352,11 +8377,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>1824</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -8391,7 +8416,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>36</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -8403,9 +8430,13 @@
       <c r="L10" s="56"/>
       <c r="M10" s="74"/>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>2</v>
+      </c>
       <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
+      <c r="Q10" s="72">
+        <v>1</v>
+      </c>
       <c r="R10" s="73"/>
       <c r="S10" s="56"/>
       <c r="T10" s="59">
@@ -8414,11 +8445,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -8453,15 +8484,21 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -8472,15 +8509,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -8513,7 +8550,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>720+72+63+1008+16+1440+576+60</f>
+        <v>3955</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -8523,24 +8563,36 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="M12" s="64">
+        <v>13</v>
+      </c>
+      <c r="N12" s="65">
+        <v>14</v>
+      </c>
+      <c r="O12" s="66">
+        <v>15</v>
+      </c>
+      <c r="P12" s="67">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>15</v>
+      </c>
+      <c r="R12" s="68">
+        <v>20</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>95996</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3999.8333333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -8582,7 +8634,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -8605,11 +8659,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -8826,7 +8880,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -8849,11 +8905,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -8947,7 +9003,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -8970,11 +9028,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -9008,7 +9066,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -9031,11 +9091,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -9069,7 +9129,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -9092,11 +9154,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -9130,7 +9192,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -9153,11 +9217,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -9200,7 +9264,10 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <f>16+1</f>
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -9210,11 +9277,17 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>10</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="71">
+        <v>10</v>
+      </c>
       <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="Q23" s="72">
+        <v>10</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
@@ -9223,11 +9296,11 @@
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -9270,7 +9343,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -9293,11 +9368,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -9331,17 +9406,26 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>63+59+1</f>
+        <v>123</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>2</v>
+      </c>
       <c r="N25" s="75"/>
       <c r="O25" s="71"/>
       <c r="P25" s="72"/>
@@ -9350,15 +9434,15 @@
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3011</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>125.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -9373,7 +9457,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>20</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -9396,11 +9482,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -9458,7 +9544,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+32</f>
+        <v>96</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -9468,9 +9557,13 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
       <c r="Q28" s="72"/>
       <c r="R28" s="73"/>
@@ -9481,11 +9574,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -9505,7 +9598,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>10</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -9528,11 +9623,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -9543,7 +9638,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>57</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -9555,9 +9652,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -9566,11 +9667,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -9581,7 +9682,10 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="71"/>
+      <c r="C31" s="71">
+        <f>10+4</f>
+        <v>14</v>
+      </c>
       <c r="D31" s="71"/>
       <c r="E31" s="71"/>
       <c r="F31" s="71"/>
@@ -9593,7 +9697,9 @@
       <c r="L31" s="56"/>
       <c r="M31" s="74"/>
       <c r="N31" s="75"/>
-      <c r="O31" s="71"/>
+      <c r="O31" s="71">
+        <v>1</v>
+      </c>
       <c r="P31" s="72"/>
       <c r="Q31" s="72"/>
       <c r="R31" s="73"/>
@@ -9604,11 +9710,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -9657,7 +9763,9 @@
       <c r="B33" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="71"/>
+      <c r="C33" s="71">
+        <v>3</v>
+      </c>
       <c r="D33" s="71"/>
       <c r="E33" s="71"/>
       <c r="F33" s="71"/>
@@ -9680,11 +9788,11 @@
       </c>
       <c r="U33" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V33" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -9695,34 +9803,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>61+72</f>
+        <v>133</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
+      <c r="M34" s="74">
+        <v>10</v>
+      </c>
+      <c r="N34" s="75">
+        <v>12</v>
+      </c>
       <c r="O34" s="71"/>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3497</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>145.70833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -9809,34 +9930,47 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>324+68+2376+1512</f>
+        <v>4280</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>112</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>41</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>64</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>26990</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4498.333333333333</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -9848,7 +9982,10 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <f>16+2</f>
+        <v>18</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -9862,7 +9999,9 @@
       <c r="N38" s="75"/>
       <c r="O38" s="71"/>
       <c r="P38" s="72"/>
-      <c r="Q38" s="72"/>
+      <c r="Q38" s="72">
+        <v>1</v>
+      </c>
       <c r="R38" s="73"/>
       <c r="S38" s="56"/>
       <c r="T38" s="76">
@@ -9871,11 +10010,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -9915,34 +10054,45 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>504+51</f>
+        <v>555</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>1</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>13392</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>558</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -9953,7 +10103,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1344+87</f>
+        <v>1431</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
@@ -9963,11 +10116,17 @@
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>3</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>7</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
@@ -9976,11 +10135,11 @@
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>17472</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10020,34 +10179,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>216+5940+8424+5400+4644+12+7128</f>
+        <v>31764</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>4*6+4</f>
+        <v>28</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>325</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>356</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>350</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>197368</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>32894.666666666664</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10125,7 +10301,9 @@
       <c r="B46" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="71"/>
+      <c r="C46" s="71">
+        <v>4</v>
+      </c>
       <c r="D46" s="71"/>
       <c r="E46" s="71"/>
       <c r="F46" s="71"/>
@@ -10148,11 +10326,11 @@
       </c>
       <c r="U46" s="76">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V46" s="76">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10163,7 +10341,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>22+2268+44</f>
+        <v>2334</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -10171,26 +10352,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>4</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14116</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2352.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -10201,7 +10392,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -10224,11 +10417,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -10315,7 +10508,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -10338,11 +10533,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -10391,7 +10586,10 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <f>4+2</f>
+        <v>6</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -10414,11 +10612,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -10544,7 +10742,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>45160</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -10558,56 +10756,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>444</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>757</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>386707</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>46675.541666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -10615,17 +10813,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="95" t="s">
+      <c r="C60" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="96"/>
-      <c r="E60" s="96"/>
-      <c r="F60" s="96"/>
-      <c r="G60" s="96"/>
-      <c r="H60" s="96"/>
-      <c r="I60" s="96"/>
-      <c r="J60" s="96"/>
-      <c r="K60" s="97"/>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="104"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -10934,25 +11132,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="98" t="s">
+      <c r="I1" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -10960,17 +11158,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="C4" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="101"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -10990,13 +11188,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="102" t="s">
+      <c r="T4" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="104" t="s">
+      <c r="U4" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="98" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11036,10 +11234,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="101"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11047,9 +11245,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="99"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13536,17 +13734,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="95" t="s">
+      <c r="C60" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="96"/>
-      <c r="E60" s="96"/>
-      <c r="F60" s="96"/>
-      <c r="G60" s="96"/>
-      <c r="H60" s="96"/>
-      <c r="I60" s="96"/>
-      <c r="J60" s="96"/>
-      <c r="K60" s="97"/>
+      <c r="D60" s="103"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="103"/>
+      <c r="G60" s="103"/>
+      <c r="H60" s="103"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="104"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F91FC4-71A8-473F-95F3-0B0D421BB222}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A636911-D668-40F1-A67D-463E0E00E82F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -16,12 +16,14 @@
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
     <sheet name="03-02-20261" sheetId="33" r:id="rId2"/>
     <sheet name="03-04-2026" sheetId="30" r:id="rId3"/>
-    <sheet name="03-06-2026" sheetId="31" r:id="rId4"/>
+    <sheet name="03-05-2026" sheetId="34" r:id="rId4"/>
+    <sheet name="03-06-2026" sheetId="31" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03-04-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'03-06-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'03-05-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'03-06-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="75">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -260,6 +262,12 @@
   </si>
   <si>
     <t>DATE: 03/04/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/06/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/05/2026</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1238,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1522,6 +1530,9 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1923,21 +1934,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1949,17 +1960,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -1979,13 +1990,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2025,10 +2036,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="101"/>
+      <c r="K5" s="102"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2036,9 +2047,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4569,17 +4580,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="102" t="s">
+      <c r="C62" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="103"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="103"/>
-      <c r="G62" s="103"/>
-      <c r="H62" s="103"/>
-      <c r="I62" s="103"/>
-      <c r="J62" s="103"/>
-      <c r="K62" s="104"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="105"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4888,21 +4899,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4914,17 +4925,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4944,13 +4955,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -4990,10 +5001,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="101"/>
+      <c r="K5" s="102"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5001,9 +5012,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7691,17 +7702,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8010,21 +8021,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8036,17 +8047,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8066,13 +8077,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8112,10 +8123,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="101"/>
+      <c r="K5" s="102"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8123,9 +8134,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10813,17 +10824,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11093,6 +11104,3116 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADCC7BF-D8DE-45DD-AFA6-3473D86FD0E5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="112" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="102"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="98"/>
+      <c r="Q6" s="98"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53">
+        <f>21+41</f>
+        <v>62</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>21</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>1605</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>66.875</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60">
+        <f>15+63+22</f>
+        <v>100</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2448</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>102</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71">
+        <v>51</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71">
+        <v>17</v>
+      </c>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1632</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>68</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71">
+        <v>23</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71">
+        <v>13</v>
+      </c>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>864</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60">
+        <f>720+72+60+63+936+60+1440+576</f>
+        <v>3927</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64">
+        <v>13</v>
+      </c>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66">
+        <v>11</v>
+      </c>
+      <c r="P12" s="67">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>7</v>
+      </c>
+      <c r="R12" s="68">
+        <v>13</v>
+      </c>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>95010</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>3958.75</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>120</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>5</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74">
+        <v>10</v>
+      </c>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71">
+        <v>10</v>
+      </c>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72">
+        <v>10</v>
+      </c>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>1128</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>168</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71">
+        <f>59+63</f>
+        <v>122</v>
+      </c>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74">
+        <v>1</v>
+      </c>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>2963</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>123.45833333333333</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71">
+        <v>16</v>
+      </c>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71">
+        <v>4</v>
+      </c>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>480</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71">
+        <f>64+30</f>
+        <v>94</v>
+      </c>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74">
+        <v>1</v>
+      </c>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>2328</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>97</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71">
+        <v>10</v>
+      </c>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71">
+        <v>57</v>
+      </c>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>1440</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71">
+        <v>4</v>
+      </c>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71">
+        <v>11</v>
+      </c>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>360</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71">
+        <v>3</v>
+      </c>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71">
+        <f>61+72</f>
+        <v>133</v>
+      </c>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75">
+        <v>12</v>
+      </c>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>3257</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>135.70833333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60">
+        <f>324+63+2376+1512</f>
+        <v>4275</v>
+      </c>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66">
+        <v>41</v>
+      </c>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67">
+        <v>35</v>
+      </c>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>26114</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>4352.333333333333</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71">
+        <v>13</v>
+      </c>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71">
+        <v>5</v>
+      </c>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>432</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60">
+        <f>504+51</f>
+        <v>555</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67">
+        <v>1</v>
+      </c>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>13392</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85">
+        <f>1344+82</f>
+        <v>1426</v>
+      </c>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89">
+        <v>2</v>
+      </c>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85">
+        <v>7</v>
+      </c>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>17400</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4644+6696</f>
+        <v>31104</v>
+      </c>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>6*4+4</f>
+        <v>28</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64">
+        <v>398</v>
+      </c>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66">
+        <v>258</v>
+      </c>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67">
+        <v>80</v>
+      </c>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>598</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>191638</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>31939.666666666668</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71">
+        <v>4</v>
+      </c>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>96</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66">
+        <f>22+2268+44</f>
+        <v>2334</v>
+      </c>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64">
+        <v>1</v>
+      </c>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>14098</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>2349.6666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71">
+        <v>6</v>
+      </c>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>144</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>44405</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>604</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>427</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>394</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>164</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>731</v>
+      </c>
+      <c r="U58" s="95">
+        <f>SUM(U7:U57)</f>
+        <v>378377</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>45497.458333333336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="103" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A2F5F4-C5DF-4049-87CE-B29D5D492895}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -11132,25 +14253,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -11158,17 +14279,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
+      <c r="D4" s="107"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="109"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11188,13 +14309,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="109" t="s">
+      <c r="T4" s="110" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="112" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="98" t="s">
+      <c r="V4" s="99" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11234,10 +14355,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="101"/>
+      <c r="K5" s="102"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11245,9 +14366,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="99"/>
+      <c r="T5" s="111"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="100"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13734,17 +16855,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="102" t="s">
+      <c r="C60" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="103"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="103"/>
-      <c r="G60" s="103"/>
-      <c r="H60" s="103"/>
-      <c r="I60" s="103"/>
-      <c r="J60" s="103"/>
-      <c r="K60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="105"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A636911-D668-40F1-A67D-463E0E00E82F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF63A8A-FCFF-46B3-B6FE-BE18FEE4219F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -18,12 +18,14 @@
     <sheet name="03-04-2026" sheetId="30" r:id="rId3"/>
     <sheet name="03-05-2026" sheetId="34" r:id="rId4"/>
     <sheet name="03-06-2026" sheetId="31" r:id="rId5"/>
+    <sheet name="03-07-2026" sheetId="35" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'03-04-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'03-05-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03-06-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'03-07-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="76">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -269,6 +271,9 @@
   <si>
     <t>DATE: 03/05/2026</t>
   </si>
+  <si>
+    <t>DATE: 03/07/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -279,7 +284,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,6 +374,22 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1238,7 +1259,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1534,6 +1555,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1578,6 +1602,24 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1934,21 +1976,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -1960,43 +2002,43 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="120" t="s">
         <v>61</v>
       </c>
       <c r="O4" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="120" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="120" t="s">
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2030,16 +2072,16 @@
       <c r="E5" s="40"/>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="117" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2047,9 +2089,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4580,17 +4622,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="103" t="s">
+      <c r="C62" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
-      <c r="J62" s="104"/>
-      <c r="K62" s="105"/>
+      <c r="D62" s="105"/>
+      <c r="E62" s="105"/>
+      <c r="F62" s="105"/>
+      <c r="G62" s="105"/>
+      <c r="H62" s="105"/>
+      <c r="I62" s="105"/>
+      <c r="J62" s="105"/>
+      <c r="K62" s="106"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4899,21 +4941,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4925,17 +4967,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4955,13 +4997,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5001,10 +5043,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="103"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5012,9 +5054,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7702,17 +7744,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8021,21 +8063,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8047,17 +8089,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8077,13 +8119,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8123,10 +8165,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="103"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8134,9 +8176,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10824,17 +10866,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11143,21 +11185,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11169,17 +11211,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11199,13 +11241,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11245,10 +11287,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="103"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11256,9 +11298,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13934,17 +13976,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14196,13 +14238,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -14253,21 +14295,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="107" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14279,43 +14321,43 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="109"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="120" t="s">
         <v>61</v>
       </c>
       <c r="O4" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="120" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="120" t="s">
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="110" t="s">
+      <c r="T4" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="112" t="s">
+      <c r="U4" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="99" t="s">
+      <c r="V4" s="100" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14349,16 +14391,16 @@
       <c r="E5" s="40"/>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="117" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="40" t="s">
+      <c r="I5" s="117" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="101" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="102"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14366,9 +14408,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="100"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="101"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14445,34 +14487,51 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <f>21+41</f>
+        <v>62</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>66.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -14507,7 +14566,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -14521,7 +14583,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -14530,11 +14594,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -14569,7 +14633,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>50</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -14581,7 +14647,9 @@
       <c r="L9" s="56"/>
       <c r="M9" s="74"/>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>1</v>
+      </c>
       <c r="P9" s="72"/>
       <c r="Q9" s="72"/>
       <c r="R9" s="73"/>
@@ -14592,11 +14660,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -14631,7 +14699,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>22</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -14643,7 +14713,9 @@
       <c r="L10" s="56"/>
       <c r="M10" s="74"/>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
       <c r="R10" s="73"/>
@@ -14654,11 +14726,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -14693,15 +14765,21 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -14712,15 +14790,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -14753,7 +14831,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>576+72+720+60+63+936+45+1440</f>
+        <v>3912</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -14763,24 +14844,34 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
+      <c r="M12" s="64">
+        <v>3</v>
+      </c>
       <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="O12" s="66">
+        <v>4</v>
+      </c>
+      <c r="P12" s="67">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>22</v>
+      </c>
+      <c r="R12" s="68">
+        <v>13</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>94602</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3941.75</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -14822,7 +14913,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -14845,11 +14938,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -15066,7 +15159,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -15089,11 +15184,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -15187,7 +15282,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -15210,11 +15307,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -15248,7 +15345,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -15271,11 +15370,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -15309,7 +15408,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -15332,11 +15433,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -15370,7 +15471,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -15393,11 +15496,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -15440,7 +15543,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -15450,11 +15555,17 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>8</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="71">
+        <v>10</v>
+      </c>
       <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="Q23" s="72">
+        <v>10</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
@@ -15463,11 +15574,11 @@
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -15510,7 +15621,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -15533,11 +15646,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -15571,13 +15684,20 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>63+59</f>
+        <v>122</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
@@ -15590,15 +15710,15 @@
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2939</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>122.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -15613,7 +15733,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>16</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -15636,11 +15758,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -15698,7 +15820,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+24</f>
+        <v>88</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -15708,11 +15833,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>1</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>4</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -15721,11 +15852,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -15745,7 +15876,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>10</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -15768,11 +15901,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -15783,7 +15916,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>57</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -15795,9 +15930,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -15806,11 +15945,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -15821,7 +15960,9 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="71"/>
+      <c r="C31" s="71">
+        <v>4</v>
+      </c>
       <c r="D31" s="71"/>
       <c r="E31" s="71"/>
       <c r="F31" s="71"/>
@@ -15844,11 +15985,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -15935,34 +16076,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>61+72</f>
+        <v>133</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
       <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
+      <c r="N34" s="75">
+        <v>12</v>
+      </c>
       <c r="O34" s="71"/>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3257</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>135.70833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16049,34 +16201,45 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>216+53+2376+1512</f>
+        <v>4157</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
       <c r="M37" s="64"/>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>17</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>143</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>25910</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4318.333333333333</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -16088,7 +16251,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>12</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -16111,11 +16276,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -16136,11 +16301,11 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="53"/>
       <c r="R39" s="81"/>
       <c r="S39" s="56"/>
       <c r="T39" s="84"/>
@@ -16155,34 +16320,45 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>50+504</f>
+        <v>554</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>13392</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>558</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -16193,7 +16369,10 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1344+82</f>
+        <v>1426</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
@@ -16203,11 +16382,17 @@
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>2</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>6</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
@@ -16216,11 +16401,11 @@
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>17388</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16260,34 +16445,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4644+6372</f>
+        <v>30780</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>4*6+4</f>
+        <v>28</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>56</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>85</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>296</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>187900</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>31316.666666666668</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -16403,7 +16605,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>44+22+2268</f>
+        <v>2334</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -16411,26 +16616,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>1</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14098</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2349.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -16441,7 +16656,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -16464,11 +16681,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -16555,7 +16772,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -16578,11 +16797,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -16631,7 +16850,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -16654,11 +16875,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -16784,7 +17005,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>43937</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -16798,56 +17019,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>731</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>372479</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>44758.458333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -16855,17 +17076,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="103" t="s">
+      <c r="C60" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="105"/>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17132,4 +17353,2925 @@
     <brk id="24" max="80" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2E0F61-5435-441A-AE16-8829F017334A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="107" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="110"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="111" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="102" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="103"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="101"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="99"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="104" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="105"/>
+      <c r="E60" s="105"/>
+      <c r="F60" s="105"/>
+      <c r="G60" s="105"/>
+      <c r="H60" s="105"/>
+      <c r="I60" s="105"/>
+      <c r="J60" s="105"/>
+      <c r="K60" s="106"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
 </file>
--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF63A8A-FCFF-46B3-B6FE-BE18FEE4219F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE330EA-7D0C-45A2-8AE2-5D320E4F6F6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -18,7 +18,9 @@
     <sheet name="03-04-2026" sheetId="30" r:id="rId3"/>
     <sheet name="03-05-2026" sheetId="34" r:id="rId4"/>
     <sheet name="03-06-2026" sheetId="31" r:id="rId5"/>
-    <sheet name="03-07-2026" sheetId="35" r:id="rId6"/>
+    <sheet name="03-07-2026" sheetId="36" r:id="rId6"/>
+    <sheet name="03-09-2026" sheetId="35" r:id="rId7"/>
+    <sheet name="03-10-2026" sheetId="37" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -26,6 +28,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'03-05-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'03-06-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'03-07-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'03-09-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'03-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="78">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -274,6 +278,12 @@
   <si>
     <t>DATE: 03/07/2026</t>
   </si>
+  <si>
+    <t>DATE: 03/09/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/10/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -409,7 +419,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -1252,6 +1262,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1259,7 +1278,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1558,16 +1577,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,29 +1625,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1976,21 +2001,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2002,43 +2027,43 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="120" t="s">
+      <c r="N4" s="102" t="s">
         <v>61</v>
       </c>
       <c r="O4" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="120" t="s">
+      <c r="P4" s="102" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="120" t="s">
+      <c r="R4" s="102" t="s">
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2072,16 +2097,16 @@
       <c r="E5" s="40"/>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="117" t="s">
+      <c r="H5" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="117" t="s">
+      <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="106"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2089,9 +2114,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4622,17 +4647,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="104" t="s">
+      <c r="C62" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="105"/>
-      <c r="E62" s="105"/>
-      <c r="F62" s="105"/>
-      <c r="G62" s="105"/>
-      <c r="H62" s="105"/>
-      <c r="I62" s="105"/>
-      <c r="J62" s="105"/>
-      <c r="K62" s="106"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
+      <c r="J62" s="108"/>
+      <c r="K62" s="109"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4941,21 +4966,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4967,17 +4992,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -4997,13 +5022,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="113" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5043,10 +5068,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5054,9 +5079,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7744,17 +7769,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8063,21 +8088,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8089,17 +8114,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8119,13 +8144,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="113" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8165,10 +8190,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8176,9 +8201,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10866,17 +10891,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11185,21 +11210,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11211,17 +11236,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11241,13 +11266,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="113" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11287,10 +11312,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11298,9 +11323,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13976,17 +14001,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14295,21 +14320,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14321,43 +14346,43 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="N4" s="120" t="s">
+      <c r="N4" s="102" t="s">
         <v>61</v>
       </c>
       <c r="O4" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="120" t="s">
+      <c r="P4" s="102" t="s">
         <v>61</v>
       </c>
       <c r="Q4" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="120" t="s">
+      <c r="R4" s="102" t="s">
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="115" t="s">
+      <c r="U4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14391,16 +14416,16 @@
       <c r="E5" s="40"/>
       <c r="F5" s="40"/>
       <c r="G5" s="40"/>
-      <c r="H5" s="117" t="s">
+      <c r="H5" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="117" t="s">
+      <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="106"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14408,9 +14433,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17076,17 +17101,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17356,6 +17381,3121 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89B154A-467C-45B6-A794-26411351FB9A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="119"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53">
+        <f>21+41</f>
+        <v>62</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>21</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>1605</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>66.875</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2448</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>102</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71">
+        <v>33</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74">
+        <v>2</v>
+      </c>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71">
+        <v>1</v>
+      </c>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72">
+        <v>15</v>
+      </c>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>1224</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>51</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71">
+        <v>6</v>
+      </c>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74">
+        <v>1</v>
+      </c>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72">
+        <v>15</v>
+      </c>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>552</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60">
+        <f>72+720+60+63+936+20+1440+576</f>
+        <v>3887</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64">
+        <v>13</v>
+      </c>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66">
+        <v>9</v>
+      </c>
+      <c r="P12" s="67">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>19</v>
+      </c>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>94277</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>3928.2083333333335</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>120</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>5</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>408</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74">
+        <v>8</v>
+      </c>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71">
+        <v>10</v>
+      </c>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72">
+        <v>10</v>
+      </c>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>840</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71">
+        <f>58+63</f>
+        <v>121</v>
+      </c>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74">
+        <v>1</v>
+      </c>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>2939</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>122.45833333333333</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71">
+        <v>16</v>
+      </c>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>384</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71">
+        <f>64+23</f>
+        <v>87</v>
+      </c>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72">
+        <v>4</v>
+      </c>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>2280</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>95</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71">
+        <v>10</v>
+      </c>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71">
+        <f>57</f>
+        <v>57</v>
+      </c>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>1440</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71">
+        <v>2</v>
+      </c>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72">
+        <v>2</v>
+      </c>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71">
+        <f>60+72</f>
+        <v>132</v>
+      </c>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
+      <c r="N34" s="75">
+        <v>12</v>
+      </c>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>3257</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>135.70833333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60">
+        <f>108+2376+1512+15</f>
+        <v>4011</v>
+      </c>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64">
+        <v>25</v>
+      </c>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66">
+        <v>30</v>
+      </c>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67">
+        <v>140</v>
+      </c>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>25244</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>4207.333333333333</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71">
+        <v>12</v>
+      </c>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>288</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="122"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60">
+        <f>504+50</f>
+        <v>554</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>13392</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85">
+        <f>1344+67</f>
+        <v>1411</v>
+      </c>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89">
+        <v>5</v>
+      </c>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85">
+        <v>8</v>
+      </c>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>17268</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4644+5184+107</f>
+        <v>29699</v>
+      </c>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>4*6+4</f>
+        <v>28</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64">
+        <v>320</v>
+      </c>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66">
+        <v>410</v>
+      </c>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67">
+        <v>433</v>
+      </c>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>598</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>185770</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>30961.666666666668</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66">
+        <f>18+44+2268</f>
+        <v>2330</v>
+      </c>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64">
+        <v>5</v>
+      </c>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>14098</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>2349.6666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>120</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>42628</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>44</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>604</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>384</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>479</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>671</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>718</v>
+      </c>
+      <c r="U58" s="95">
+        <f>SUM(U7:U57)</f>
+        <v>369238</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>44268.916666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE2E0F61-5435-441A-AE16-8829F017334A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17395,25 +20535,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="107" t="s">
+      <c r="I1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -17421,17 +20561,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="108"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17451,13 +20591,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="114" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="113" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="100" t="s">
+      <c r="V4" s="103" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17497,10 +20637,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="102" t="s">
+      <c r="J5" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="103"/>
+      <c r="K5" s="119"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17508,9 +20648,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="101"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -19997,17 +23137,2938 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="104" t="s">
+      <c r="C60" s="107" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="105"/>
-      <c r="E60" s="105"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="105"/>
-      <c r="H60" s="105"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="106"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC59979F-B1E4-46BE-B2CF-4B5C9EB1EDDA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="120" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="119"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="104"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="109"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE330EA-7D0C-45A2-8AE2-5D320E4F6F6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B60001-BD37-4EAF-8292-385A4ECF23C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -1586,6 +1586,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1642,9 +1645,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2001,21 +2001,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2027,17 +2027,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2057,13 +2057,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2103,10 +2103,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="105" t="s">
+      <c r="J5" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="106"/>
+      <c r="K5" s="107"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2114,9 +2114,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4647,17 +4647,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="107" t="s">
+      <c r="C62" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="108"/>
-      <c r="E62" s="108"/>
-      <c r="F62" s="108"/>
-      <c r="G62" s="108"/>
-      <c r="H62" s="108"/>
-      <c r="I62" s="108"/>
-      <c r="J62" s="108"/>
-      <c r="K62" s="109"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="109"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="109"/>
+      <c r="H62" s="109"/>
+      <c r="I62" s="109"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="110"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4966,21 +4966,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4992,17 +4992,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5022,13 +5022,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5068,10 +5068,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5079,9 +5079,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7769,17 +7769,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8088,21 +8088,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8114,17 +8114,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8144,13 +8144,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8190,10 +8190,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8201,9 +8201,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10891,17 +10891,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11210,21 +11210,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11236,17 +11236,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11266,13 +11266,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11312,10 +11312,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11323,9 +11323,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14001,17 +14001,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14320,21 +14320,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14346,17 +14346,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14376,13 +14376,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="116" t="s">
+      <c r="U4" s="117" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14422,10 +14422,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="105" t="s">
+      <c r="J5" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="106"/>
+      <c r="K5" s="107"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14433,9 +14433,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17101,17 +17101,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17420,21 +17420,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17446,17 +17446,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17476,13 +17476,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17522,10 +17522,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17533,9 +17533,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -19447,7 +19447,7 @@
       <c r="P39" s="54"/>
       <c r="Q39" s="53"/>
       <c r="R39" s="73"/>
-      <c r="S39" s="122"/>
+      <c r="S39" s="103"/>
       <c r="T39" s="76"/>
       <c r="U39" s="76"/>
       <c r="V39" s="76"/>
@@ -20216,17 +20216,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20478,13 +20478,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -20517,7 +20517,7 @@
     <col min="15" max="15" width="10" style="9" customWidth="1"/>
     <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
     <col min="17" max="17" width="10" style="9" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
     <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
@@ -20535,21 +20535,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20561,17 +20561,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20591,13 +20591,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20637,10 +20637,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20648,9 +20648,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20727,34 +20727,51 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <f>21+41</f>
+        <v>62</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1605</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>66.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -20789,7 +20806,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -20803,7 +20823,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -20812,11 +20834,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -20851,7 +20873,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>33</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -20874,11 +20898,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -20913,7 +20937,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>6</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -20925,7 +20951,9 @@
       <c r="L10" s="56"/>
       <c r="M10" s="74"/>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
       <c r="R10" s="73"/>
@@ -20936,11 +20964,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -20975,15 +21003,21 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -20994,15 +21028,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -21035,7 +21069,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>720+72+60+63+864+56+1440+576</f>
+        <v>3851</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -21045,24 +21082,32 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
+      <c r="M12" s="64">
+        <v>22</v>
+      </c>
       <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
+      <c r="O12" s="66">
+        <v>5</v>
+      </c>
+      <c r="P12" s="67">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>20</v>
+      </c>
       <c r="R12" s="68"/>
       <c r="S12" s="63"/>
-      <c r="T12" s="59">
+      <c r="T12" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>93557</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3898.2083333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -21104,7 +21149,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -21121,17 +21168,17 @@
       <c r="Q13" s="72"/>
       <c r="R13" s="73"/>
       <c r="S13" s="56"/>
-      <c r="T13" s="59">
+      <c r="T13" s="77">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -21348,7 +21395,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -21371,11 +21420,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -21469,7 +21518,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -21492,11 +21543,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -21530,7 +21581,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -21553,11 +21606,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -21591,7 +21644,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -21614,11 +21669,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -21652,7 +21707,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -21675,11 +21732,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -21722,7 +21779,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -21732,11 +21791,17 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>6</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="71">
+        <v>10</v>
+      </c>
       <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="Q23" s="72">
+        <v>9</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
@@ -21745,11 +21810,11 @@
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -21792,7 +21857,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -21815,11 +21882,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -21853,13 +21920,20 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>57+63</f>
+        <v>120</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
@@ -21872,15 +21946,15 @@
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -21895,7 +21969,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>16</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -21918,11 +21994,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -21980,7 +22056,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+19</f>
+        <v>83</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -21990,11 +22069,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>1</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>4</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -22003,11 +22088,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -22027,7 +22112,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>10</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -22050,11 +22137,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -22065,7 +22152,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>57</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -22077,9 +22166,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -22088,11 +22181,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -22103,7 +22196,9 @@
       <c r="B31" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="71"/>
+      <c r="C31" s="71">
+        <v>2</v>
+      </c>
       <c r="D31" s="71"/>
       <c r="E31" s="71"/>
       <c r="F31" s="71"/>
@@ -22126,11 +22221,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -22217,34 +22312,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>60+72</f>
+        <v>132</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
+      <c r="N34" s="75">
+        <v>12</v>
+      </c>
       <c r="O34" s="71"/>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3257</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>135.70833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22331,34 +22439,49 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>19+2376+1512</f>
+        <v>3907</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
+      <c r="L37" s="63">
+        <v>64</v>
+      </c>
+      <c r="M37" s="64">
+        <v>64</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>10</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>81</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>24380</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4063.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -22370,7 +22493,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>12</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -22393,11 +22518,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -22418,16 +22543,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -22437,34 +22562,47 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>441+61</f>
+        <v>502</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="M40" s="64">
+        <v>2</v>
+      </c>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>12192</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>508</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22475,34 +22613,47 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>6+1344</f>
+        <v>1350</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>53</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>4</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
-      <c r="R41" s="87"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
+      <c r="R41" s="87">
+        <v>9</v>
+      </c>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>17082</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1423.5</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22542,34 +22693,55 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4644+4104</f>
+        <v>28512</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="66">
+        <v>5</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>5*6+4</f>
+        <v>34</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>452</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>328</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
-      <c r="R43" s="68"/>
+      <c r="Q43" s="67">
+        <v>432</v>
+      </c>
+      <c r="R43" s="68">
+        <v>109</v>
+      </c>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>718</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>179062</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>29843.666666666668</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -22685,7 +22857,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>18+2268+44</f>
+        <v>2330</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -22693,26 +22868,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>4</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14092</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2348.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -22723,7 +22908,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -22746,11 +22933,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -22837,7 +23024,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -22860,11 +23049,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -22913,7 +23102,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -22936,11 +23127,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -23066,7 +23257,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>41183</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -23080,56 +23271,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>856</v>
       </c>
       <c r="U58" s="4">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>358450</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>42864.416666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -23137,17 +23328,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23456,21 +23647,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23482,17 +23673,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="113"/>
+      <c r="K4" s="114"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23512,13 +23703,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="114" t="s">
+      <c r="T4" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="V4" s="104" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23558,10 +23749,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="119" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="119"/>
+      <c r="K5" s="120"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23569,9 +23760,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="104"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="105"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26058,17 +26249,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="107" t="s">
+      <c r="C60" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="108"/>
-      <c r="E60" s="108"/>
-      <c r="F60" s="108"/>
-      <c r="G60" s="108"/>
-      <c r="H60" s="108"/>
-      <c r="I60" s="108"/>
-      <c r="J60" s="108"/>
-      <c r="K60" s="109"/>
+      <c r="D60" s="109"/>
+      <c r="E60" s="109"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="109"/>
+      <c r="H60" s="109"/>
+      <c r="I60" s="109"/>
+      <c r="J60" s="109"/>
+      <c r="K60" s="110"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26320,13 +26511,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B60001-BD37-4EAF-8292-385A4ECF23C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A093D02D-1DD3-4416-AD86-1C3184143AD1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="03-07-2026" sheetId="36" r:id="rId6"/>
     <sheet name="03-09-2026" sheetId="35" r:id="rId7"/>
     <sheet name="03-10-2026" sheetId="37" r:id="rId8"/>
+    <sheet name="03-11-2026" sheetId="38" r:id="rId9"/>
+    <sheet name="03-12-2026" sheetId="39" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -30,6 +32,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'03-07-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'03-09-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'03-10-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'03-11-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'03-12-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="80">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -283,6 +287,12 @@
   </si>
   <si>
     <t>DATE: 03/10/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/11/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/12/2026</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1288,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1588,6 +1598,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2001,21 +2014,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2027,17 +2040,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2057,13 +2070,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2103,10 +2116,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="106" t="s">
+      <c r="J5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="107"/>
+      <c r="K5" s="108"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2114,9 +2127,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4647,17 +4660,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="108" t="s">
+      <c r="C62" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="109"/>
-      <c r="E62" s="109"/>
-      <c r="F62" s="109"/>
-      <c r="G62" s="109"/>
-      <c r="H62" s="109"/>
-      <c r="I62" s="109"/>
-      <c r="J62" s="109"/>
-      <c r="K62" s="110"/>
+      <c r="D62" s="110"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="110"/>
+      <c r="I62" s="110"/>
+      <c r="J62" s="110"/>
+      <c r="K62" s="111"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4916,6 +4929,2927 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{503CD895-99B7-47F2-8E8B-4BB748FB001D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="121"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -4966,21 +7900,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -4992,17 +7926,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5022,13 +7956,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5068,10 +8002,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5079,9 +8013,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7769,17 +10703,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8088,21 +11022,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8114,17 +11048,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8144,13 +11078,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8190,10 +11124,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8201,9 +11135,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10891,17 +13825,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11210,21 +14144,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11236,17 +14170,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11266,13 +14200,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11312,10 +14246,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11323,9 +14257,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14001,17 +16935,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14320,21 +17254,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14346,17 +17280,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14376,13 +17310,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="117" t="s">
+      <c r="U4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14422,10 +17356,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="106" t="s">
+      <c r="J5" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="107"/>
+      <c r="K5" s="108"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14433,9 +17367,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17101,17 +20035,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17420,21 +20354,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17446,17 +20380,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17476,13 +20410,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17522,10 +20456,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17533,9 +20467,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20216,17 +23150,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20535,21 +23469,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20561,17 +23495,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20591,13 +23525,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20637,10 +23571,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20648,9 +23582,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23328,17 +26262,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23647,21 +26581,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23673,17 +26607,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23703,13 +26637,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="115" t="s">
+      <c r="T4" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="104" t="s">
+      <c r="V4" s="105" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23749,10 +26683,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="119" t="s">
+      <c r="J5" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="121"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23760,9 +26694,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="105"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23839,34 +26773,51 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <f>19+41</f>
+        <v>60</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>2</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1581</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>65.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -23901,7 +26852,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -23915,7 +26869,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -23924,11 +26880,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2448</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -23963,7 +26919,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>31</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -23973,9 +26931,13 @@
       <c r="J9" s="72"/>
       <c r="K9" s="73"/>
       <c r="L9" s="56"/>
-      <c r="M9" s="74"/>
+      <c r="M9" s="74">
+        <v>1</v>
+      </c>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>1</v>
+      </c>
       <c r="P9" s="72"/>
       <c r="Q9" s="72"/>
       <c r="R9" s="73"/>
@@ -23986,11 +26948,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -24025,7 +26987,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>5</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -24035,9 +26999,13 @@
       <c r="J10" s="72"/>
       <c r="K10" s="73"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="74"/>
+      <c r="M10" s="74">
+        <v>1</v>
+      </c>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
       <c r="R10" s="73"/>
@@ -24048,11 +27016,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -24087,15 +27055,21 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>9</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -24106,15 +27080,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -24147,7 +27121,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>576+72+720+60+63+864+10+1440</f>
+        <v>3805</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -24157,24 +27134,34 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
+      <c r="M12" s="64">
+        <v>11</v>
+      </c>
+      <c r="N12" s="65">
+        <v>19</v>
+      </c>
+      <c r="O12" s="66">
+        <v>10</v>
+      </c>
+      <c r="P12" s="67">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>15</v>
+      </c>
       <c r="R12" s="68"/>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>92224</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3842.6666666666665</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -24216,7 +27203,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -24239,11 +27228,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -24460,7 +27449,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>4</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -24483,11 +27474,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -24581,7 +27572,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -24604,11 +27597,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -24642,7 +27635,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -24665,11 +27660,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -24703,7 +27698,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>4</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -24726,11 +27723,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -24764,7 +27761,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -24787,11 +27786,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -24834,7 +27833,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -24844,11 +27845,17 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>4</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="71">
+        <v>10</v>
+      </c>
       <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="Q23" s="72">
+        <v>8</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
@@ -24857,11 +27864,11 @@
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -24904,7 +27911,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -24927,11 +27936,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -24965,34 +27974,45 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>63+54</f>
+        <v>117</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>2</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
       <c r="Q25" s="72"/>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -25007,7 +28027,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>16</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -25030,11 +28052,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -25092,7 +28114,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+17</f>
+        <v>81</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -25102,11 +28127,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>2</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -25115,11 +28146,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -25139,7 +28170,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>8</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -25149,9 +28182,13 @@
       <c r="J29" s="72"/>
       <c r="K29" s="73"/>
       <c r="L29" s="56"/>
-      <c r="M29" s="74"/>
+      <c r="M29" s="74">
+        <v>1</v>
+      </c>
       <c r="N29" s="75"/>
-      <c r="O29" s="71"/>
+      <c r="O29" s="71">
+        <v>1</v>
+      </c>
       <c r="P29" s="72"/>
       <c r="Q29" s="72"/>
       <c r="R29" s="73"/>
@@ -25162,11 +28199,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -25177,7 +28214,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>57</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -25189,9 +28228,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -25200,11 +28243,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -25225,9 +28268,13 @@
       <c r="J31" s="72"/>
       <c r="K31" s="73"/>
       <c r="L31" s="56"/>
-      <c r="M31" s="74"/>
+      <c r="M31" s="74">
+        <v>1</v>
+      </c>
       <c r="N31" s="75"/>
-      <c r="O31" s="71"/>
+      <c r="O31" s="71">
+        <v>1</v>
+      </c>
       <c r="P31" s="72"/>
       <c r="Q31" s="72"/>
       <c r="R31" s="73"/>
@@ -25238,11 +28285,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -25329,34 +28376,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>57+72</f>
+        <v>129</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3221</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>134.20833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -25443,34 +28503,47 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>2052+74+1512</f>
+        <v>3638</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>20</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>30</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>126</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>22892</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3815.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -25482,7 +28555,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>12</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -25505,11 +28580,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -25530,16 +28605,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -25549,34 +28624,47 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>441+61</f>
+        <v>502</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="M40" s="64">
+        <v>2</v>
+      </c>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>1</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>12168</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>507</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -25587,34 +28675,45 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1248+80</f>
+        <v>1328</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>5</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>10</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>12</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>16269</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1355.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -25654,34 +28753,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4644+2916</f>
+        <v>27324</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>6*6+3</f>
+        <v>39</v>
+      </c>
+      <c r="K43" s="68">
+        <f>6*93+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>326</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>272</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>337</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>170163</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>28360.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -25797,7 +28913,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>6+2268+44</f>
+        <v>2318</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -25805,26 +28924,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>10</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>9</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14092</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2348.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -25835,7 +28964,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -25858,11 +28989,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -25949,7 +29080,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -25972,11 +29105,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -26025,7 +29158,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -26048,11 +29183,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -26178,7 +29313,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>39629</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -26192,39 +29327,39 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
@@ -26233,15 +29368,15 @@
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>761</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>345689</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>41000.458333333328</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -26249,17 +29384,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="108" t="s">
+      <c r="C60" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="109"/>
-      <c r="E60" s="109"/>
-      <c r="F60" s="109"/>
-      <c r="G60" s="109"/>
-      <c r="H60" s="109"/>
-      <c r="I60" s="109"/>
-      <c r="J60" s="109"/>
-      <c r="K60" s="110"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26526,4 +29661,2925 @@
     <brk id="24" max="80" man="1"/>
   </colBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB236C6-0FF1-4950-9AC1-7191DC07D583}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="112" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="115"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="121"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="106"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="104"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="110"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="110"/>
+      <c r="G60" s="110"/>
+      <c r="H60" s="110"/>
+      <c r="I60" s="110"/>
+      <c r="J60" s="110"/>
+      <c r="K60" s="111"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
 </file>
--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A093D02D-1DD3-4416-AD86-1C3184143AD1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908FF1D2-A70F-47C6-A0ED-20BFB0377348}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="03-10-2026" sheetId="37" r:id="rId8"/>
     <sheet name="03-11-2026" sheetId="38" r:id="rId9"/>
     <sheet name="03-12-2026" sheetId="39" r:id="rId10"/>
+    <sheet name="03-13-2026" sheetId="40" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -34,6 +35,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'03-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'03-11-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'03-12-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'03-13-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="81">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -293,6 +295,9 @@
   </si>
   <si>
     <t>DATE: 03/12/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/13/2026</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1293,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1598,6 +1603,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2014,21 +2022,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2040,17 +2048,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2070,13 +2078,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2116,10 +2124,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="107" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="108"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2127,9 +2135,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4660,17 +4668,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="109" t="s">
+      <c r="C62" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="110"/>
-      <c r="E62" s="110"/>
-      <c r="F62" s="110"/>
-      <c r="G62" s="110"/>
-      <c r="H62" s="110"/>
-      <c r="I62" s="110"/>
-      <c r="J62" s="110"/>
-      <c r="K62" s="111"/>
+      <c r="D62" s="111"/>
+      <c r="E62" s="111"/>
+      <c r="F62" s="111"/>
+      <c r="G62" s="111"/>
+      <c r="H62" s="111"/>
+      <c r="I62" s="111"/>
+      <c r="J62" s="111"/>
+      <c r="K62" s="112"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4979,21 +4987,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5005,17 +5013,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5035,13 +5043,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5081,10 +5089,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5092,9 +5100,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -5171,34 +5179,50 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>56</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>4</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>63.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -5233,7 +5257,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -5256,11 +5283,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -5295,7 +5322,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>27</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -5305,11 +5334,17 @@
       <c r="J9" s="72"/>
       <c r="K9" s="73"/>
       <c r="L9" s="56"/>
-      <c r="M9" s="74"/>
+      <c r="M9" s="74">
+        <v>1</v>
+      </c>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>2</v>
+      </c>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>1</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -5318,11 +5353,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -5357,7 +5392,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>2</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -5369,9 +5406,13 @@
       <c r="L10" s="56"/>
       <c r="M10" s="74"/>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
+      <c r="Q10" s="72">
+        <v>1</v>
+      </c>
       <c r="R10" s="73"/>
       <c r="S10" s="56"/>
       <c r="T10" s="59">
@@ -5380,11 +5421,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -5419,17 +5460,25 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>8</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
-      <c r="M11" s="74"/>
+      <c r="M11" s="74">
+        <v>1</v>
+      </c>
       <c r="N11" s="75"/>
       <c r="O11" s="71"/>
       <c r="P11" s="72"/>
@@ -5438,15 +5487,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -5479,7 +5528,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>72+720+60+63+792+1440+576</f>
+        <v>3723</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -5489,24 +5541,36 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="M12" s="64">
+        <v>19</v>
+      </c>
+      <c r="N12" s="65">
+        <v>16</v>
+      </c>
+      <c r="O12" s="66">
+        <v>10</v>
+      </c>
+      <c r="P12" s="67">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>20</v>
+      </c>
+      <c r="R12" s="68">
+        <v>14</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>90566</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3773.5833333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -5548,7 +5612,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -5571,11 +5637,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -5792,7 +5858,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>3</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -5802,7 +5870,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -5815,11 +5885,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -5913,7 +5983,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -5936,11 +6008,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -5974,7 +6046,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -5997,11 +6071,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -6035,7 +6109,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>3</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -6045,7 +6121,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -6058,11 +6136,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -6096,7 +6174,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -6119,11 +6199,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -6166,7 +6246,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -6176,24 +6258,32 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>4</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>9</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>8</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -6236,7 +6326,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -6259,11 +6351,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -6297,34 +6389,47 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>63+50+2</f>
+        <v>115</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>2</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
+      <c r="Q25" s="72">
+        <v>2</v>
+      </c>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -6339,7 +6444,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>15</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -6349,7 +6456,9 @@
       <c r="J26" s="72"/>
       <c r="K26" s="73"/>
       <c r="L26" s="56"/>
-      <c r="M26" s="74"/>
+      <c r="M26" s="74">
+        <v>1</v>
+      </c>
       <c r="N26" s="75"/>
       <c r="O26" s="71"/>
       <c r="P26" s="72"/>
@@ -6362,11 +6471,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -6424,7 +6533,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+12</f>
+        <v>76</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -6434,11 +6546,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>4</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -6447,11 +6565,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -6471,7 +6589,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>6</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -6481,9 +6601,13 @@
       <c r="J29" s="72"/>
       <c r="K29" s="73"/>
       <c r="L29" s="56"/>
-      <c r="M29" s="74"/>
+      <c r="M29" s="74">
+        <v>1</v>
+      </c>
       <c r="N29" s="75"/>
-      <c r="O29" s="71"/>
+      <c r="O29" s="71">
+        <v>1</v>
+      </c>
       <c r="P29" s="72"/>
       <c r="Q29" s="72"/>
       <c r="R29" s="73"/>
@@ -6494,11 +6618,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -6509,7 +6633,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>56</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -6521,7 +6647,9 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
       <c r="Q30" s="72"/>
       <c r="R30" s="73"/>
@@ -6532,11 +6660,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -6557,7 +6685,9 @@
       <c r="J31" s="72"/>
       <c r="K31" s="73"/>
       <c r="L31" s="56"/>
-      <c r="M31" s="74"/>
+      <c r="M31" s="74">
+        <v>1</v>
+      </c>
       <c r="N31" s="75"/>
       <c r="O31" s="71"/>
       <c r="P31" s="72"/>
@@ -6570,11 +6700,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -6661,34 +6791,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>49+72</f>
+        <v>121</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>4</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3077</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>128.20833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6775,34 +6918,47 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>1944+88+1512</f>
+        <v>3544</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>45</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>50</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>100</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>22442</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3740.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -6814,7 +6970,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>11</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -6824,7 +6982,9 @@
       <c r="J38" s="72"/>
       <c r="K38" s="73"/>
       <c r="L38" s="56"/>
-      <c r="M38" s="74"/>
+      <c r="M38" s="74">
+        <v>1</v>
+      </c>
       <c r="N38" s="75"/>
       <c r="O38" s="71"/>
       <c r="P38" s="72"/>
@@ -6837,11 +6997,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -6862,16 +7022,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -6881,34 +7041,47 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>57+441</f>
+        <v>498</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="M40" s="64">
+        <v>2</v>
+      </c>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>12096</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -6919,34 +7092,43 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>53+1248</f>
+        <v>1301</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
       <c r="M41" s="89"/>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>8</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>15897</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1324.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -6986,34 +7168,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4536+648+54</f>
+        <v>25002</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>8*6+3</f>
+        <v>51</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>454</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>206</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>454</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>157317</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>26219.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -7129,7 +7328,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>6+2268+44</f>
+        <v>2318</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -7137,26 +7339,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>10</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>8</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14086</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2347.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -7167,7 +7379,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -7190,11 +7404,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -7281,7 +7495,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -7304,11 +7520,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -7357,7 +7573,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -7380,11 +7598,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -7510,7 +7728,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>37066</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -7524,56 +7742,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>790</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>329728</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>38657.166666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -7581,17 +7799,2938 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F5CCBB-02CD-417B-876A-5CAA07E5A1F2}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="117" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="121" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="122"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -7900,21 +11039,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -7926,17 +11065,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -7956,13 +11095,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8002,10 +11141,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8013,9 +11152,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10703,17 +13842,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11022,21 +14161,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11048,17 +14187,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11078,13 +14217,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11124,10 +14263,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11135,9 +14274,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13825,17 +16964,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14144,21 +17283,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14170,17 +17309,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14200,13 +17339,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14246,10 +17385,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14257,9 +17396,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -16935,17 +20074,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17254,21 +20393,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17280,17 +20419,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17310,13 +20449,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="118" t="s">
+      <c r="U4" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17356,10 +20495,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="107" t="s">
+      <c r="J5" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="108"/>
+      <c r="K5" s="109"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17367,9 +20506,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20035,17 +23174,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20354,21 +23493,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20380,17 +23519,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20410,13 +23549,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20456,10 +23595,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20467,9 +23606,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23150,17 +26289,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23469,21 +26608,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23495,17 +26634,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23525,13 +26664,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23571,10 +26710,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23582,9 +26721,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26262,17 +29401,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26581,21 +29720,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26607,17 +29746,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26637,13 +29776,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26683,10 +29822,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26694,9 +29833,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29384,17 +32523,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29703,21 +32842,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -29729,17 +32868,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="114" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="115"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="116"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29759,13 +32898,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="116" t="s">
+      <c r="T4" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="122" t="s">
+      <c r="U4" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="105" t="s">
+      <c r="V4" s="106" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29805,10 +32944,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="120" t="s">
+      <c r="J5" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="121"/>
+      <c r="K5" s="122"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29816,9 +32955,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="106"/>
+      <c r="T5" s="118"/>
+      <c r="U5" s="124"/>
+      <c r="V5" s="107"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29895,34 +33034,50 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>56</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>2</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>4</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1557</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>64.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -29957,7 +33112,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -29980,11 +33138,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -30019,7 +33177,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>28</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -30029,11 +33189,17 @@
       <c r="J9" s="72"/>
       <c r="K9" s="73"/>
       <c r="L9" s="56"/>
-      <c r="M9" s="74"/>
+      <c r="M9" s="74">
+        <v>1</v>
+      </c>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>2</v>
+      </c>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>1</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -30042,11 +33208,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -30081,7 +33247,9 @@
       <c r="B10" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="71">
+        <v>3</v>
+      </c>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
@@ -30091,11 +33259,17 @@
       <c r="J10" s="72"/>
       <c r="K10" s="73"/>
       <c r="L10" s="56"/>
-      <c r="M10" s="74"/>
+      <c r="M10" s="74">
+        <v>1</v>
+      </c>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
+      <c r="Q10" s="72">
+        <v>1</v>
+      </c>
       <c r="R10" s="73"/>
       <c r="S10" s="56"/>
       <c r="T10" s="59">
@@ -30104,11 +33278,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -30143,17 +33317,25 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>8</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
-      <c r="M11" s="74"/>
+      <c r="M11" s="74">
+        <v>1</v>
+      </c>
       <c r="N11" s="75"/>
       <c r="O11" s="71"/>
       <c r="P11" s="72"/>
@@ -30162,15 +33344,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -30203,7 +33385,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>72+720+60+63+792+33+1440+576</f>
+        <v>3756</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -30213,24 +33398,36 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="M12" s="64">
+        <v>20</v>
+      </c>
+      <c r="N12" s="65">
+        <v>13</v>
+      </c>
+      <c r="O12" s="66">
+        <v>12</v>
+      </c>
+      <c r="P12" s="67">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>22</v>
+      </c>
+      <c r="R12" s="68">
+        <v>4</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>91472</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3811.3333333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -30272,7 +33469,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -30295,11 +33494,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -30516,7 +33715,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>3</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -30526,7 +33727,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -30539,11 +33742,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -30637,7 +33840,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -30660,11 +33865,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -30698,7 +33903,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -30721,11 +33928,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -30759,7 +33966,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>3</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -30769,7 +33978,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -30782,11 +33993,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -30820,7 +34031,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -30843,11 +34056,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -30890,7 +34103,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -30900,24 +34115,32 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>4</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>9</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>8</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -30960,7 +34183,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -30983,11 +34208,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -31021,34 +34246,47 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>50+63</f>
+        <v>113</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>4</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
+      <c r="Q25" s="72">
+        <v>2</v>
+      </c>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -31063,7 +34301,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>15</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -31073,7 +34313,9 @@
       <c r="J26" s="72"/>
       <c r="K26" s="73"/>
       <c r="L26" s="56"/>
-      <c r="M26" s="74"/>
+      <c r="M26" s="74">
+        <v>1</v>
+      </c>
       <c r="N26" s="75"/>
       <c r="O26" s="71"/>
       <c r="P26" s="72"/>
@@ -31086,11 +34328,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -31148,7 +34390,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>64+14</f>
+        <v>78</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -31158,11 +34403,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>4</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>1</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -31171,11 +34422,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -31195,7 +34446,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>6</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -31205,11 +34458,17 @@
       <c r="J29" s="72"/>
       <c r="K29" s="73"/>
       <c r="L29" s="56"/>
-      <c r="M29" s="74"/>
+      <c r="M29" s="74">
+        <v>1</v>
+      </c>
       <c r="N29" s="75"/>
-      <c r="O29" s="71"/>
+      <c r="O29" s="71">
+        <v>1</v>
+      </c>
       <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
+      <c r="Q29" s="72">
+        <v>2</v>
+      </c>
       <c r="R29" s="73"/>
       <c r="S29" s="56"/>
       <c r="T29" s="59">
@@ -31218,11 +34477,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -31233,7 +34492,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>56</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -31245,9 +34506,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>2</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -31256,11 +34521,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -31281,7 +34546,9 @@
       <c r="J31" s="72"/>
       <c r="K31" s="73"/>
       <c r="L31" s="56"/>
-      <c r="M31" s="74"/>
+      <c r="M31" s="74">
+        <v>1</v>
+      </c>
       <c r="N31" s="75"/>
       <c r="O31" s="71"/>
       <c r="P31" s="72"/>
@@ -31294,11 +34561,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -31385,34 +34652,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>53+72</f>
+        <v>125</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>4</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3173</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>132.20833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31499,34 +34779,45 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>2052+45+1512</f>
+        <v>3609</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
       <c r="M37" s="64"/>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>30</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>105</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>22472</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3745.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -31538,7 +34829,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>11</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -31548,7 +34841,9 @@
       <c r="J38" s="72"/>
       <c r="K38" s="73"/>
       <c r="L38" s="56"/>
-      <c r="M38" s="74"/>
+      <c r="M38" s="74">
+        <v>1</v>
+      </c>
       <c r="N38" s="75"/>
       <c r="O38" s="71"/>
       <c r="P38" s="72"/>
@@ -31561,11 +34856,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -31586,16 +34881,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -31605,34 +34900,47 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>59+441</f>
+        <v>500</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="M40" s="64">
+        <v>2</v>
+      </c>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>12144</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -31643,34 +34951,45 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1248+68</f>
+        <v>1316</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>2</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>8</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>16101</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1341.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31710,34 +35029,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+4536+1728+88</f>
+        <v>26116</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>6*6+3</f>
+        <v>39</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>346</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>393</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>440</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>164379</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>27396.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31853,7 +35189,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>6+2268+44</f>
+        <v>2318</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -31861,26 +35200,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>10</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>9</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14092</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2348.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -31891,7 +35240,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -31914,11 +35265,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -32005,7 +35356,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -32028,11 +35381,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -32081,7 +35434,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -32104,11 +35459,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -32234,7 +35589,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>38301</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -32248,56 +35603,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>772</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>338296</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>39909.916666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -32305,17 +35660,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="109" t="s">
+      <c r="C60" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="110"/>
-      <c r="F60" s="110"/>
-      <c r="G60" s="110"/>
-      <c r="H60" s="110"/>
-      <c r="I60" s="110"/>
-      <c r="J60" s="110"/>
-      <c r="K60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="111"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
+      <c r="J60" s="111"/>
+      <c r="K60" s="112"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32567,13 +35922,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908FF1D2-A70F-47C6-A0ED-20BFB0377348}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE03DC0-C679-4F1D-9601-30526BCDBE50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="9" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="03-10-2026" sheetId="37" r:id="rId8"/>
     <sheet name="03-11-2026" sheetId="38" r:id="rId9"/>
     <sheet name="03-12-2026" sheetId="39" r:id="rId10"/>
-    <sheet name="03-13-2026" sheetId="40" r:id="rId11"/>
+    <sheet name="03-14-2026" sheetId="40" r:id="rId11"/>
+    <sheet name="03-15-2026" sheetId="41" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -35,10 +36,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'03-10-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'03-11-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'03-12-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'03-13-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'03-14-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'03-15-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -54,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="82">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -297,7 +300,10 @@
     <t>DATE: 03/12/2026</t>
   </si>
   <si>
-    <t>DATE: 03/13/2026</t>
+    <t>DATE: 03/14/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/15/2026</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1299,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1603,6 +1609,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2022,21 +2031,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2048,17 +2057,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2078,13 +2087,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2124,10 +2133,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="110"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2135,9 +2144,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4668,17 +4677,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="110" t="s">
+      <c r="C62" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="111"/>
-      <c r="I62" s="111"/>
-      <c r="J62" s="111"/>
-      <c r="K62" s="112"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="112"/>
+      <c r="F62" s="112"/>
+      <c r="G62" s="112"/>
+      <c r="H62" s="112"/>
+      <c r="I62" s="112"/>
+      <c r="J62" s="112"/>
+      <c r="K62" s="113"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4987,21 +4996,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5013,17 +5022,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5043,13 +5052,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5089,10 +5098,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5100,9 +5109,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7799,17 +7808,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8118,21 +8127,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8144,17 +8153,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8174,13 +8183,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8220,10 +8229,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8231,9 +8240,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -8310,34 +8319,50 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>56</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>4</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1533</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>63.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -8372,7 +8397,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -8395,11 +8423,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -8434,7 +8462,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>25</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -8444,11 +8474,17 @@
       <c r="J9" s="72"/>
       <c r="K9" s="73"/>
       <c r="L9" s="56"/>
-      <c r="M9" s="74"/>
+      <c r="M9" s="74">
+        <v>1</v>
+      </c>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>2</v>
+      </c>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>2</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -8457,11 +8493,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -8508,9 +8544,13 @@
       <c r="L10" s="56"/>
       <c r="M10" s="74"/>
       <c r="N10" s="75"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="71">
+        <v>1</v>
+      </c>
       <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
+      <c r="Q10" s="72">
+        <v>2</v>
+      </c>
       <c r="R10" s="73"/>
       <c r="S10" s="56"/>
       <c r="T10" s="59">
@@ -8519,11 +8559,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -8558,17 +8598,25 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>8</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
-      <c r="M11" s="74"/>
+      <c r="M11" s="74">
+        <v>1</v>
+      </c>
       <c r="N11" s="75"/>
       <c r="O11" s="71"/>
       <c r="P11" s="72"/>
@@ -8577,15 +8625,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -8618,7 +8666,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>576+72+720+63+60+720+12+1440</f>
+        <v>3663</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -8628,24 +8679,36 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="M12" s="64">
+        <v>25</v>
+      </c>
+      <c r="N12" s="65">
+        <v>16</v>
+      </c>
+      <c r="O12" s="66">
+        <v>12</v>
+      </c>
+      <c r="P12" s="67">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>26</v>
+      </c>
+      <c r="R12" s="68">
+        <v>10</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>89465</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3727.7083333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -8687,7 +8750,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -8710,11 +8775,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -8931,7 +8996,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>3</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -8941,7 +9008,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -8954,11 +9023,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -9052,7 +9121,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -9075,11 +9146,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -9113,7 +9184,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -9136,11 +9209,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -9174,7 +9247,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>3</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -9184,7 +9259,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -9197,11 +9274,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -9235,7 +9312,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -9258,11 +9337,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -9305,7 +9384,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -9315,24 +9396,32 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>4</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>9</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>8</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -9375,7 +9464,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -9398,11 +9489,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -9436,34 +9527,47 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>2+63+50</f>
+        <v>115</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>2</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
+      <c r="Q25" s="72">
+        <v>2</v>
+      </c>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2891</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -9478,7 +9582,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>15</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -9488,7 +9594,9 @@
       <c r="J26" s="72"/>
       <c r="K26" s="73"/>
       <c r="L26" s="56"/>
-      <c r="M26" s="74"/>
+      <c r="M26" s="74">
+        <v>1</v>
+      </c>
       <c r="N26" s="75"/>
       <c r="O26" s="71"/>
       <c r="P26" s="72"/>
@@ -9501,11 +9609,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -9563,7 +9671,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>8+64</f>
+        <v>72</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -9573,11 +9684,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>5</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -9586,11 +9703,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -9610,7 +9727,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>6</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -9620,9 +9739,13 @@
       <c r="J29" s="72"/>
       <c r="K29" s="73"/>
       <c r="L29" s="56"/>
-      <c r="M29" s="74"/>
+      <c r="M29" s="74">
+        <v>1</v>
+      </c>
       <c r="N29" s="75"/>
-      <c r="O29" s="71"/>
+      <c r="O29" s="71">
+        <v>1</v>
+      </c>
       <c r="P29" s="72"/>
       <c r="Q29" s="72"/>
       <c r="R29" s="73"/>
@@ -9633,11 +9756,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -9648,7 +9771,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>56</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -9660,7 +9785,9 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
       <c r="Q30" s="72"/>
       <c r="R30" s="73"/>
@@ -9671,11 +9798,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -9696,7 +9823,9 @@
       <c r="J31" s="72"/>
       <c r="K31" s="73"/>
       <c r="L31" s="56"/>
-      <c r="M31" s="74"/>
+      <c r="M31" s="74">
+        <v>1</v>
+      </c>
       <c r="N31" s="75"/>
       <c r="O31" s="71"/>
       <c r="P31" s="72"/>
@@ -9709,11 +9838,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -9800,34 +9929,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>37+72</f>
+        <v>109</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>4</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2789</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>116.20833333333333</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -9914,34 +10056,47 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>18+1944+1512</f>
+        <v>3474</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>41</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>30</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>70</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>21698</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3616.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -9953,7 +10108,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>10</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -9963,7 +10120,9 @@
       <c r="J38" s="72"/>
       <c r="K38" s="73"/>
       <c r="L38" s="56"/>
-      <c r="M38" s="74"/>
+      <c r="M38" s="74">
+        <v>1</v>
+      </c>
       <c r="N38" s="75"/>
       <c r="O38" s="71"/>
       <c r="P38" s="72"/>
@@ -9976,11 +10135,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -10020,34 +10179,47 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>56+441</f>
+        <v>497</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="M40" s="64">
+        <v>2</v>
+      </c>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>3</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>12096</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -10058,34 +10230,43 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1248+33</f>
+        <v>1281</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
       <c r="M41" s="89"/>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>8</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>20</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>15717</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1309.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10125,34 +10306,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+3672+19+1</f>
+        <v>23456</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>9*6+3</f>
+        <v>57</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>571</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>376</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>523</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>150183</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>25030.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -10268,7 +10466,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>6+2268+44</f>
+        <v>2318</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -10276,26 +10477,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>10</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>8</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14086</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2347.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -10306,7 +10517,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -10329,11 +10542,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -10420,7 +10633,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -10443,11 +10658,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -10496,7 +10711,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -10519,11 +10736,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -10649,7 +10866,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>35348</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -10663,56 +10880,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>679</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>799</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>320137</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>37265.291666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -10720,17 +10937,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -10982,13 +11199,2934 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EBCA50-CEE7-4E30-B84B-F667B2AF4E21}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="118" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="124" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="107" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="123"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="106"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -11039,21 +14177,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11065,17 +14203,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11095,13 +14233,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11141,10 +14279,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11152,9 +14290,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -13842,17 +16980,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14161,21 +17299,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14187,17 +17325,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14217,13 +17355,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14263,10 +17401,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14274,9 +17412,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -16964,17 +20102,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17283,21 +20421,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17309,17 +20447,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17339,13 +20477,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17385,10 +20523,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17396,9 +20534,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20074,17 +23212,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20393,21 +23531,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20419,17 +23557,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20449,13 +23587,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="119" t="s">
+      <c r="U4" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20495,10 +23633,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="108" t="s">
+      <c r="J5" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="109"/>
+      <c r="K5" s="110"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20506,9 +23644,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="121"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23174,17 +26312,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23493,21 +26631,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23519,17 +26657,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23549,13 +26687,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23595,10 +26733,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23606,9 +26744,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26289,17 +29427,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26608,21 +29746,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26634,17 +29772,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26664,13 +29802,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26710,10 +29848,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26721,9 +29859,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29401,17 +32539,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29720,21 +32858,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -29746,17 +32884,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29776,13 +32914,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29822,10 +32960,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29833,9 +32971,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32523,17 +35661,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32842,21 +35980,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="113" t="s">
+      <c r="I1" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -32868,17 +36006,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="116"/>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -32898,13 +36036,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="117" t="s">
+      <c r="T4" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="106" t="s">
+      <c r="V4" s="107" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -32944,10 +36082,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="121" t="s">
+      <c r="J5" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="122"/>
+      <c r="K5" s="123"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -32955,9 +36093,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="107"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="108"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35660,17 +38798,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="110" t="s">
+      <c r="C60" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="111"/>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="112"/>
+      <c r="D60" s="112"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="112"/>
+      <c r="G60" s="112"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
+      <c r="J60" s="112"/>
+      <c r="K60" s="113"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE03DC0-C679-4F1D-9601-30526BCDBE50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B2A685-7F2D-48BC-ABF3-06EA17B109F9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="10" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="11" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -24,7 +24,8 @@
     <sheet name="03-11-2026" sheetId="38" r:id="rId9"/>
     <sheet name="03-12-2026" sheetId="39" r:id="rId10"/>
     <sheet name="03-14-2026" sheetId="40" r:id="rId11"/>
-    <sheet name="03-15-2026" sheetId="41" r:id="rId12"/>
+    <sheet name="03-16-2026" sheetId="41" r:id="rId12"/>
+    <sheet name="03-17-2026" sheetId="42" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -37,11 +38,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">'03-11-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'03-12-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'03-14-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'03-15-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'03-16-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'03-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="83">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -304,6 +305,9 @@
   </si>
   <si>
     <t>DATE: 03/15/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/16/2026</t>
   </si>
 </sst>
 </file>
@@ -1299,7 +1303,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1609,6 +1613,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2031,21 +2038,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2057,17 +2064,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2087,13 +2094,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2133,10 +2140,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="111"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2144,9 +2151,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4677,17 +4684,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="111" t="s">
+      <c r="C62" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="112"/>
-      <c r="E62" s="112"/>
-      <c r="F62" s="112"/>
-      <c r="G62" s="112"/>
-      <c r="H62" s="112"/>
-      <c r="I62" s="112"/>
-      <c r="J62" s="112"/>
-      <c r="K62" s="113"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="113"/>
+      <c r="H62" s="113"/>
+      <c r="I62" s="113"/>
+      <c r="J62" s="113"/>
+      <c r="K62" s="114"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -4996,21 +5003,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5022,17 +5029,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5052,13 +5059,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5098,10 +5105,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5109,9 +5116,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7808,17 +7815,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8127,21 +8134,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8153,17 +8160,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8183,13 +8190,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8229,10 +8236,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8240,9 +8247,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10937,17 +10944,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11256,25 +11263,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -11282,17 +11289,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11312,13 +11319,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11358,10 +11365,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11369,9 +11376,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -11448,34 +11455,50 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>55</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>1</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>4</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1509</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>62.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -11510,7 +11533,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>22+63+15</f>
+        <v>100</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -11533,11 +11559,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -11572,7 +11598,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>23</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -11584,9 +11612,13 @@
       <c r="L9" s="56"/>
       <c r="M9" s="74"/>
       <c r="N9" s="75"/>
-      <c r="O9" s="71"/>
+      <c r="O9" s="71">
+        <v>1</v>
+      </c>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>2</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -11595,11 +11627,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -11648,7 +11680,9 @@
       <c r="N10" s="75"/>
       <c r="O10" s="71"/>
       <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
+      <c r="Q10" s="72">
+        <v>2</v>
+      </c>
       <c r="R10" s="73"/>
       <c r="S10" s="56"/>
       <c r="T10" s="59">
@@ -11657,11 +11691,11 @@
       </c>
       <c r="U10" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V10" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="50"/>
       <c r="AF10" s="12"/>
@@ -11696,17 +11730,25 @@
       <c r="B11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="71">
+        <v>8</v>
+      </c>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
-      <c r="M11" s="74"/>
+      <c r="M11" s="74">
+        <v>1</v>
+      </c>
       <c r="N11" s="75"/>
       <c r="O11" s="71"/>
       <c r="P11" s="72"/>
@@ -11715,15 +11757,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -11756,7 +11798,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>576+72+60+63+720+648+66+1440</f>
+        <v>3645</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -11766,24 +11811,36 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="M12" s="64">
+        <v>5</v>
+      </c>
+      <c r="N12" s="65">
+        <v>12</v>
+      </c>
+      <c r="O12" s="66">
+        <v>17</v>
+      </c>
+      <c r="P12" s="67">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>20</v>
+      </c>
+      <c r="R12" s="68">
+        <v>22</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>88530</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3688.75</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -11825,7 +11882,9 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>5</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
@@ -11848,11 +11907,11 @@
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -12069,7 +12128,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>3</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -12079,7 +12140,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -12092,11 +12155,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -12190,7 +12253,9 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>4</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
@@ -12213,11 +12278,11 @@
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -12251,7 +12316,9 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>6</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
@@ -12274,11 +12341,11 @@
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -12312,7 +12379,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>3</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -12322,7 +12391,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -12335,11 +12406,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -12373,7 +12444,9 @@
       <c r="B22" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="71"/>
+      <c r="C22" s="71">
+        <v>2</v>
+      </c>
       <c r="D22" s="71"/>
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
@@ -12396,11 +12469,11 @@
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -12443,7 +12516,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -12453,24 +12528,32 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>4</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>9</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>8</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -12513,7 +12596,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>7</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -12536,11 +12621,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -12574,34 +12659,47 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <f>2+49+63</f>
+        <v>114</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>2</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
+      <c r="Q25" s="72">
+        <v>2</v>
+      </c>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2867</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>119.45833333333333</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -12616,7 +12714,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>15</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -12626,7 +12726,9 @@
       <c r="J26" s="72"/>
       <c r="K26" s="73"/>
       <c r="L26" s="56"/>
-      <c r="M26" s="74"/>
+      <c r="M26" s="74">
+        <v>1</v>
+      </c>
       <c r="N26" s="75"/>
       <c r="O26" s="71"/>
       <c r="P26" s="72"/>
@@ -12639,11 +12741,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -12701,7 +12803,10 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <f>8+63</f>
+        <v>71</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -12711,11 +12816,17 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>3</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>2</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>5</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -12724,11 +12835,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1944</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -12748,7 +12859,9 @@
       <c r="B29" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="71"/>
+      <c r="C29" s="71">
+        <v>6</v>
+      </c>
       <c r="D29" s="71"/>
       <c r="E29" s="71"/>
       <c r="F29" s="71"/>
@@ -12771,11 +12884,11 @@
       </c>
       <c r="U29" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V29" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:54" x14ac:dyDescent="0.25">
@@ -12786,7 +12899,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>56</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -12798,7 +12913,9 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
       <c r="P30" s="72"/>
       <c r="Q30" s="72"/>
       <c r="R30" s="73"/>
@@ -12809,11 +12926,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -12834,7 +12951,9 @@
       <c r="J31" s="72"/>
       <c r="K31" s="73"/>
       <c r="L31" s="56"/>
-      <c r="M31" s="74"/>
+      <c r="M31" s="74">
+        <v>1</v>
+      </c>
       <c r="N31" s="75"/>
       <c r="O31" s="71"/>
       <c r="P31" s="72"/>
@@ -12847,11 +12966,11 @@
       </c>
       <c r="U31" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V31" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -12938,34 +13057,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>34+72</f>
+        <v>106</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>1</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>4</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2717</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>113.20833333333333</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13052,34 +13184,47 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>1836+83+1512</f>
+        <v>3431</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
       <c r="G37" s="60"/>
-      <c r="H37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>5</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>40</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>54</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>21188</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3531.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -13091,7 +13236,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>10</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -13101,7 +13248,9 @@
       <c r="J38" s="72"/>
       <c r="K38" s="73"/>
       <c r="L38" s="56"/>
-      <c r="M38" s="74"/>
+      <c r="M38" s="74">
+        <v>1</v>
+      </c>
       <c r="N38" s="75"/>
       <c r="O38" s="71"/>
       <c r="P38" s="72"/>
@@ -13114,11 +13263,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -13158,34 +13307,47 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>441+56</f>
+        <v>497</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
-      <c r="M40" s="64"/>
+      <c r="M40" s="64">
+        <v>2</v>
+      </c>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>3</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>12096</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -13196,34 +13358,43 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>10+1248</f>
+        <v>1258</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
       <c r="M41" s="89"/>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>5</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>14</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>15333</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1277.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13263,34 +13434,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+5400+2808</f>
+        <v>22572</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="66">
+        <v>5</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>10*6+4</f>
+        <v>64</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>3</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>513</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>530</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>142347</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>23724.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -13406,7 +13596,10 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>2268+1+44</f>
+        <v>2313</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
@@ -13414,26 +13607,36 @@
       <c r="H47" s="66"/>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
       <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
+      <c r="M47" s="64">
+        <v>10</v>
+      </c>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>6</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14044</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2340.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -13444,7 +13647,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -13467,11 +13672,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -13558,7 +13763,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -13581,11 +13788,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -13634,7 +13841,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -13657,11 +13866,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -13787,7 +13996,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>34367</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -13801,56 +14010,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>812</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>310142</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>35784.333333333328</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -13858,17 +14067,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14127,6 +14336,2927 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECCF1771-D6A3-45ED-9E59-C97409F9D00A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="115" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="125" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="124"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -14177,21 +17307,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14203,17 +17333,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14233,13 +17363,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14279,10 +17409,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14290,9 +17420,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -16980,17 +20110,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17299,21 +20429,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17325,17 +20455,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17355,13 +20485,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17401,10 +20531,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17412,9 +20542,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20102,17 +23232,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20421,21 +23551,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20447,17 +23577,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20477,13 +23607,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20523,10 +23653,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20534,9 +23664,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23212,17 +26342,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23531,21 +26661,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23557,17 +26687,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23587,13 +26717,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="120" t="s">
+      <c r="U4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23633,10 +26763,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="109" t="s">
+      <c r="J5" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="110"/>
+      <c r="K5" s="111"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23644,9 +26774,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="122"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26312,17 +29442,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26631,21 +29761,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26657,17 +29787,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26687,13 +29817,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26733,10 +29863,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26744,9 +29874,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29427,17 +32557,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29746,21 +32876,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -29772,17 +32902,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29802,13 +32932,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29848,10 +32978,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29859,9 +32989,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32539,17 +35669,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32858,21 +35988,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -32884,17 +36014,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -32914,13 +36044,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -32960,10 +36090,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -32971,9 +36101,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35661,17 +38791,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -35980,21 +39110,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="114" t="s">
+      <c r="I1" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="114"/>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="114"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="114"/>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
-      <c r="S1" s="114"/>
-      <c r="T1" s="114"/>
-      <c r="U1" s="114"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36006,17 +39136,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="115" t="s">
+      <c r="C4" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="117"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="118"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36036,13 +39166,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="118" t="s">
+      <c r="T4" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="124" t="s">
+      <c r="U4" s="125" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="107" t="s">
+      <c r="V4" s="108" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36082,10 +39212,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="122" t="s">
+      <c r="J5" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="123"/>
+      <c r="K5" s="124"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36093,9 +39223,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="125"/>
-      <c r="V5" s="108"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="126"/>
+      <c r="V5" s="109"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -38798,17 +41928,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="111" t="s">
+      <c r="C60" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="112"/>
-      <c r="E60" s="112"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="114"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B2A685-7F2D-48BC-ABF3-06EA17B109F9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF90376A-1B02-4917-9DDB-3EDE88A63CDE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="11" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="13" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -26,6 +26,8 @@
     <sheet name="03-14-2026" sheetId="40" r:id="rId11"/>
     <sheet name="03-16-2026" sheetId="41" r:id="rId12"/>
     <sheet name="03-17-2026" sheetId="42" r:id="rId13"/>
+    <sheet name="03-18-2026" sheetId="43" r:id="rId14"/>
+    <sheet name="03-19-2026" sheetId="44" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -40,6 +42,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'03-14-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'03-16-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'03-17-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'03-18-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'03-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -58,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="85">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -308,6 +312,12 @@
   </si>
   <si>
     <t>DATE: 03/16/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/18/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/19/2026</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1313,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1613,6 +1623,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2038,21 +2051,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2064,17 +2077,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2094,13 +2107,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2140,10 +2153,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="110" t="s">
+      <c r="J5" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="111"/>
+      <c r="K5" s="112"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2151,9 +2164,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4684,17 +4697,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="112" t="s">
+      <c r="C62" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="113"/>
-      <c r="E62" s="113"/>
-      <c r="F62" s="113"/>
-      <c r="G62" s="113"/>
-      <c r="H62" s="113"/>
-      <c r="I62" s="113"/>
-      <c r="J62" s="113"/>
-      <c r="K62" s="114"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="114"/>
+      <c r="F62" s="114"/>
+      <c r="G62" s="114"/>
+      <c r="H62" s="114"/>
+      <c r="I62" s="114"/>
+      <c r="J62" s="114"/>
+      <c r="K62" s="115"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5003,21 +5016,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5029,17 +5042,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5059,13 +5072,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5105,10 +5118,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5116,9 +5129,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7815,17 +7828,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8134,21 +8147,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8160,17 +8173,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8190,13 +8203,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8236,10 +8249,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8247,9 +8260,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10944,17 +10957,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11263,21 +11276,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11289,17 +11302,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11319,13 +11332,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11365,10 +11378,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11376,9 +11389,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14067,17 +14080,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14386,21 +14399,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14412,17 +14425,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14442,13 +14455,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14488,10 +14501,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14499,9 +14512,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -16988,17 +17001,6061 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41EE18DA-50BA-446D-A669-D0F3DA86ED1F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="124" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="125"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53">
+        <v>42</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57">
+        <v>11</v>
+      </c>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>2</v>
+      </c>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>21</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>1389</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>57.875</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60">
+        <f>10+63+15</f>
+        <v>88</v>
+      </c>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64">
+        <v>5</v>
+      </c>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2280</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>95</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71">
+        <v>11</v>
+      </c>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74">
+        <v>5</v>
+      </c>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>384</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>16</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74">
+        <v>3</v>
+      </c>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60">
+        <f>72+720+60+63+576+70+1440+576</f>
+        <v>3577</v>
+      </c>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64">
+        <v>5</v>
+      </c>
+      <c r="N12" s="65">
+        <v>6</v>
+      </c>
+      <c r="O12" s="66">
+        <v>15</v>
+      </c>
+      <c r="P12" s="67">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>20</v>
+      </c>
+      <c r="R12" s="68">
+        <v>14</v>
+      </c>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>86839</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>3618.2916666666665</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71">
+        <v>3</v>
+      </c>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74">
+        <v>1</v>
+      </c>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>96</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>4</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74">
+        <v>2</v>
+      </c>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71">
+        <v>3</v>
+      </c>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74">
+        <v>1</v>
+      </c>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71">
+        <f>1+5</f>
+        <v>6</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71">
+        <v>2</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74">
+        <v>2</v>
+      </c>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71">
+        <v>1</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71">
+        <v>17</v>
+      </c>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74">
+        <v>4</v>
+      </c>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71">
+        <v>9</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>8</v>
+      </c>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>931</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>38.791666666666664</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71">
+        <v>6</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71">
+        <v>54</v>
+      </c>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74">
+        <v>42</v>
+      </c>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72">
+        <v>2</v>
+      </c>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>2387</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>99.458333333333329</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71">
+        <v>7</v>
+      </c>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74">
+        <v>6</v>
+      </c>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>312</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71">
+        <v>6</v>
+      </c>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74">
+        <v>28</v>
+      </c>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72">
+        <v>4</v>
+      </c>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>912</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71">
+        <v>44</v>
+      </c>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74">
+        <v>10</v>
+      </c>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71">
+        <v>2</v>
+      </c>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>1344</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71">
+        <f>4+72</f>
+        <v>76</v>
+      </c>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74">
+        <v>11</v>
+      </c>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72">
+        <v>4</v>
+      </c>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>2237</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>93.208333333333329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60">
+        <f>1512+1512</f>
+        <v>3024</v>
+      </c>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60">
+        <v>2</v>
+      </c>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62">
+        <v>6</v>
+      </c>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64">
+        <v>45</v>
+      </c>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66">
+        <v>24</v>
+      </c>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67">
+        <v>111</v>
+      </c>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>19232</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>3205.3333333333335</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71">
+        <v>8</v>
+      </c>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74">
+        <v>1</v>
+      </c>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>216</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60">
+        <f>441+27</f>
+        <v>468</v>
+      </c>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64">
+        <v>12</v>
+      </c>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>11616</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85">
+        <f>23+1152</f>
+        <v>1175</v>
+      </c>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89">
+        <v>21</v>
+      </c>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85">
+        <v>5</v>
+      </c>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86">
+        <v>15</v>
+      </c>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>14601</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>1216.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66">
+        <f>5940+8424+5292+3672+1836</f>
+        <v>25164</v>
+      </c>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66">
+        <v>2</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>11*6+1</f>
+        <v>67</v>
+      </c>
+      <c r="K43" s="68">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64">
+        <v>356</v>
+      </c>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66">
+        <v>450</v>
+      </c>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67">
+        <v>554</v>
+      </c>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>639</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>159783</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>26630.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66">
+        <f>2268+35</f>
+        <v>2303</v>
+      </c>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68">
+        <v>6</v>
+      </c>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64">
+        <v>10</v>
+      </c>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66">
+        <v>6</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>13984</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>2330.6666666666665</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>24</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>120</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>36127</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>55</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>67</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>604</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>581</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>517</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>46</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>734</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>801</v>
+      </c>
+      <c r="U58" s="95">
+        <f>SUM(U7:U57)</f>
+        <v>319587</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>38074.875</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E0DDB1-C2C1-437F-82FE-1324F6CC2192}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="120" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="126" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="124" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="125"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17307,21 +23364,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17333,17 +23390,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17363,13 +23420,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17409,10 +23466,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17420,9 +23477,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20110,17 +26167,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20429,21 +26486,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20455,17 +26512,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20485,13 +26542,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20531,10 +26588,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20542,9 +26599,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23232,17 +29289,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23551,21 +29608,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23577,17 +29634,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23607,13 +29664,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23653,10 +29710,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23664,9 +29721,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26342,17 +32399,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26661,21 +32718,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26687,17 +32744,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26717,13 +32774,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="121" t="s">
+      <c r="U4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26763,10 +32820,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="110" t="s">
+      <c r="J5" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="111"/>
+      <c r="K5" s="112"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26774,9 +32831,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="122"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29442,17 +35499,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29761,21 +35818,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -29787,17 +35844,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29817,13 +35874,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29863,10 +35920,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29874,9 +35931,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32557,17 +38614,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32876,21 +38933,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -32902,17 +38959,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -32932,13 +38989,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -32978,10 +39035,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -32989,9 +39046,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35669,17 +41726,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -35988,21 +42045,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36014,17 +42071,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36044,13 +42101,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36090,10 +42147,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36101,9 +42158,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -38791,17 +44848,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39110,21 +45167,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="115" t="s">
+      <c r="I1" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39136,17 +45193,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="118"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="119"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39166,13 +45223,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="119" t="s">
+      <c r="T4" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="108" t="s">
+      <c r="V4" s="109" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39212,10 +45269,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="123" t="s">
+      <c r="J5" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="124"/>
+      <c r="K5" s="125"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39223,9 +45280,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="109"/>
+      <c r="T5" s="121"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="110"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -41928,17 +47985,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="112" t="s">
+      <c r="C60" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
+      <c r="F60" s="114"/>
+      <c r="G60" s="114"/>
+      <c r="H60" s="114"/>
+      <c r="I60" s="114"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="115"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0B74EB-3C3C-4ED0-A556-1FDEEC19D88B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B424368A-C6EA-4234-89C9-7FEFAFD0DD27}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="17" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -30,7 +30,8 @@
     <sheet name="03-19-2026" sheetId="44" r:id="rId15"/>
     <sheet name="03-20-2026" sheetId="45" r:id="rId16"/>
     <sheet name="03-23-2026" sheetId="46" r:id="rId17"/>
-    <sheet name="03-22-2026" sheetId="47" r:id="rId18"/>
+    <sheet name="03-24-2026" sheetId="47" r:id="rId18"/>
+    <sheet name="03-25-2026" sheetId="48" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -48,8 +49,9 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'03-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">'03-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'03-20-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'03-22-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'03-23-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'03-24-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'03-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="89">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -329,10 +331,13 @@
     <t>DATE: 03/20/2026</t>
   </si>
   <si>
-    <t>DATE: 03/22/2026</t>
+    <t>DATE: 03/23/2026</t>
   </si>
   <si>
-    <t>DATE: 03/23/2026</t>
+    <t>DATE: 03/24/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/25/2026</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1333,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1638,6 +1643,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2069,21 +2077,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2095,17 +2103,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2125,13 +2133,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2171,10 +2179,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="112" t="s">
+      <c r="J5" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="113"/>
+      <c r="K5" s="114"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2182,9 +2190,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -4715,17 +4723,17 @@
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="114" t="s">
+      <c r="C62" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="115"/>
-      <c r="E62" s="115"/>
-      <c r="F62" s="115"/>
-      <c r="G62" s="115"/>
-      <c r="H62" s="115"/>
-      <c r="I62" s="115"/>
-      <c r="J62" s="115"/>
-      <c r="K62" s="116"/>
+      <c r="D62" s="116"/>
+      <c r="E62" s="116"/>
+      <c r="F62" s="116"/>
+      <c r="G62" s="116"/>
+      <c r="H62" s="116"/>
+      <c r="I62" s="116"/>
+      <c r="J62" s="116"/>
+      <c r="K62" s="117"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5034,21 +5042,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5060,17 +5068,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5090,13 +5098,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5136,10 +5144,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5147,9 +5155,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7846,17 +7854,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8165,21 +8173,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8191,17 +8199,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8221,13 +8229,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8267,10 +8275,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8278,9 +8286,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -10975,17 +10983,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11294,21 +11302,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11320,17 +11328,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11350,13 +11358,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11396,10 +11404,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11407,9 +11415,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14098,17 +14106,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14417,21 +14425,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14443,17 +14451,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14473,13 +14481,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14519,10 +14527,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14530,9 +14538,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17019,17 +17027,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17338,21 +17346,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17364,17 +17372,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17394,13 +17402,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17440,10 +17448,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17451,9 +17459,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20142,17 +20150,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20461,21 +20469,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20487,17 +20495,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20517,13 +20525,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20563,10 +20571,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20574,9 +20582,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23252,17 +23260,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23571,21 +23579,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23597,17 +23605,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23627,13 +23635,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23673,10 +23681,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23684,9 +23692,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26359,17 +26367,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26678,25 +26686,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -26704,17 +26712,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26734,13 +26742,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26780,10 +26788,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26791,9 +26799,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29476,17 +29484,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29795,25 +29803,25 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -29821,17 +29829,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29851,13 +29859,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29897,10 +29905,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29908,9 +29916,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29987,34 +29995,48 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>38</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
       <c r="M7" s="57"/>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>2</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>42.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -30049,7 +30071,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>1+8+63+15</f>
+        <v>87</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -30063,7 +30088,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>2</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -30072,11 +30099,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2136</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -30111,7 +30138,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>5</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -30134,11 +30163,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -30240,10 +30269,14 @@
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -30254,15 +30287,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -30295,7 +30328,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>72+720+60+63+432+50+1440+576</f>
+        <v>3413</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -30305,24 +30341,36 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="M12" s="64">
+        <v>36</v>
+      </c>
+      <c r="N12" s="65">
+        <v>11</v>
+      </c>
+      <c r="O12" s="66">
+        <v>11</v>
+      </c>
+      <c r="P12" s="67">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>20</v>
+      </c>
+      <c r="R12" s="68">
+        <v>12</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>83558</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3481.5833333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -30364,12 +30412,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>2</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="H13" s="71">
+        <v>16</v>
+      </c>
       <c r="I13" s="71"/>
       <c r="J13" s="72"/>
       <c r="K13" s="73"/>
@@ -30383,15 +30435,15 @@
       <c r="S13" s="56"/>
       <c r="T13" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -30608,7 +30660,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>2</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -30618,7 +30672,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -30631,11 +30687,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -30729,12 +30785,16 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>2</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="H19" s="71">
+        <v>20</v>
+      </c>
       <c r="I19" s="71"/>
       <c r="J19" s="72"/>
       <c r="K19" s="73"/>
@@ -30748,15 +30808,15 @@
       <c r="S19" s="56"/>
       <c r="T19" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -30790,12 +30850,16 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>5</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
       <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="H20" s="71">
+        <v>16</v>
+      </c>
       <c r="I20" s="71"/>
       <c r="J20" s="72"/>
       <c r="K20" s="73"/>
@@ -30809,15 +30873,15 @@
       <c r="S20" s="56"/>
       <c r="T20" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -30851,7 +30915,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>2</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -30861,7 +30927,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -30874,11 +30942,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -30917,7 +30985,9 @@
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
       <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="H22" s="71">
+        <v>20</v>
+      </c>
       <c r="I22" s="71"/>
       <c r="J22" s="72"/>
       <c r="K22" s="73"/>
@@ -30931,15 +31001,15 @@
       <c r="S22" s="56"/>
       <c r="T22" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -30982,7 +31052,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>35</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -30994,22 +31066,28 @@
       <c r="L23" s="56"/>
       <c r="M23" s="74"/>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>1</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>2</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -31052,7 +31130,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>6</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -31075,11 +31155,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -31113,34 +31193,46 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <v>40</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>1</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
+      <c r="Q25" s="72">
+        <v>2</v>
+      </c>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1067</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>44.458333333333336</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -31155,7 +31247,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>7</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -31178,11 +31272,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -31240,7 +31334,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <v>63</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -31263,11 +31359,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -31325,7 +31421,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>43</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -31337,9 +31435,13 @@
       <c r="L30" s="56"/>
       <c r="M30" s="74"/>
       <c r="N30" s="75"/>
-      <c r="O30" s="71"/>
+      <c r="O30" s="71">
+        <v>1</v>
+      </c>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -31348,11 +31450,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -31477,34 +31579,45 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>67+4</f>
+        <v>71</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
       <c r="M34" s="74"/>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>3</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1829</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>76.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31591,7 +31704,10 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>972+47+1512</f>
+        <v>2531</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
@@ -31599,26 +31715,34 @@
       <c r="H37" s="60"/>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>2</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>28</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>39</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>90</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>16130</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>2688.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -31630,7 +31754,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>8</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -31653,11 +31779,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -31697,34 +31823,45 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>20+1+378</f>
+        <v>399</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>9672</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -31735,34 +31872,45 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1056+57</f>
+        <v>1113</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>5</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>4</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>19</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>13701</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1141.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31802,34 +31950,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5940+8424+432+4536+6480+1728</f>
+        <v>27540</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="66">
+        <v>5</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>6*13</f>
+        <v>78</v>
+      </c>
+      <c r="K43" s="68">
+        <f>21*6+2</f>
+        <v>128</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>590</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>424</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>543</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>174800</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>29133.333333333332</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -31945,34 +32112,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>2268+29</f>
+        <v>2297</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
       <c r="G47" s="66"/>
-      <c r="H47" s="66"/>
+      <c r="H47" s="66">
+        <v>2</v>
+      </c>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>4</v>
+      </c>
       <c r="L47" s="63"/>
       <c r="M47" s="64"/>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>5</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>13882</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2313.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -31983,7 +32163,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -32006,11 +32188,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -32097,7 +32279,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -32120,11 +32304,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -32173,7 +32357,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -32196,11 +32382,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -32326,7 +32512,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>37749</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -32340,56 +32526,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>662</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>453</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>322755</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>39645.999999999993</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -32397,17 +32583,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32666,6 +32852,2927 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956C393D-A9F7-456B-9502-F2AABC9F6E8D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="119" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="122" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="128" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="111" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="126" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="127"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -32716,21 +35823,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -32742,17 +35849,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -32772,13 +35879,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -32818,10 +35925,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -32829,9 +35936,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35519,17 +38626,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -35838,21 +38945,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -35864,17 +38971,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -35894,13 +39001,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -35940,10 +39047,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -35951,9 +39058,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -38641,17 +41748,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -38960,21 +42067,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -38986,17 +42093,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39016,13 +42123,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39062,10 +42169,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39073,9 +42180,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -41751,17 +44858,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -42070,21 +45177,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42096,17 +45203,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42126,13 +45233,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="123" t="s">
+      <c r="U4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42172,10 +45279,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="112" t="s">
+      <c r="J5" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="113"/>
+      <c r="K5" s="114"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42183,9 +45290,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="124"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -44851,17 +47958,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -45170,21 +48277,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45196,17 +48303,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45226,13 +48333,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45272,10 +48379,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45283,9 +48390,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -47966,17 +51073,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -48285,21 +51392,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -48311,17 +51418,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -48341,13 +51448,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -48387,10 +51494,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48398,9 +51505,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -51078,17 +54185,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -51397,21 +54504,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -51423,17 +54530,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -51453,13 +54560,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -51499,10 +54606,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -51510,9 +54617,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -54200,17 +57307,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -54519,21 +57626,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="117" t="s">
+      <c r="I1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="117"/>
-      <c r="P1" s="117"/>
-      <c r="Q1" s="117"/>
-      <c r="R1" s="117"/>
-      <c r="S1" s="117"/>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -54545,17 +57652,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="120"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="121"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -54575,13 +57682,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="121" t="s">
+      <c r="T4" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="127" t="s">
+      <c r="U4" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="110" t="s">
+      <c r="V4" s="111" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -54621,10 +57728,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="126" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="126"/>
+      <c r="K5" s="127"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -54632,9 +57739,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="122"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="111"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="112"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -57337,17 +60444,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="114" t="s">
+      <c r="C60" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="115"/>
-      <c r="E60" s="115"/>
-      <c r="F60" s="115"/>
-      <c r="G60" s="115"/>
-      <c r="H60" s="115"/>
-      <c r="I60" s="115"/>
-      <c r="J60" s="115"/>
-      <c r="K60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="116"/>
+      <c r="H60" s="116"/>
+      <c r="I60" s="116"/>
+      <c r="J60" s="116"/>
+      <c r="K60" s="117"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747693C4-D55C-471C-B86F-71F5BDD3963E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD447EA1-1EDE-4071-BA99-865A3682E361}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="03-26-2026" sheetId="49" r:id="rId20"/>
     <sheet name="03-27-2026" sheetId="50" r:id="rId21"/>
     <sheet name="03-28-2026" sheetId="51" r:id="rId22"/>
+    <sheet name="03-29-2026" sheetId="52" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'03-02-20261'!$A$1:$W$59</definedName>
@@ -58,7 +59,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="19">'03-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'03-27-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'03-28-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'03-29-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="93">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -353,6 +355,9 @@
   </si>
   <si>
     <t>DATE: 03/28/2026</t>
+  </si>
+  <si>
+    <t>DATE: 03/29/2026</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1353,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1658,6 +1663,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="64" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2095,21 +2103,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -2121,17 +2129,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -2151,13 +2159,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -2197,10 +2205,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -2208,9 +2216,9 @@
       <c r="Q5" s="93"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -3983,11 +3991,11 @@
       <c r="O39" s="53"/>
       <c r="P39" s="54"/>
       <c r="Q39" s="53"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -4736,22 +4744,22 @@
       <c r="U60" s="97"/>
       <c r="V60" s="97"/>
     </row>
-    <row r="61" spans="1:22" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C62" s="116" t="s">
+      <c r="C62" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="117"/>
-      <c r="E62" s="117"/>
-      <c r="F62" s="117"/>
-      <c r="G62" s="117"/>
-      <c r="H62" s="117"/>
-      <c r="I62" s="117"/>
-      <c r="J62" s="117"/>
-      <c r="K62" s="118"/>
+      <c r="D62" s="118"/>
+      <c r="E62" s="118"/>
+      <c r="F62" s="118"/>
+      <c r="G62" s="118"/>
+      <c r="H62" s="118"/>
+      <c r="I62" s="118"/>
+      <c r="J62" s="118"/>
+      <c r="K62" s="119"/>
       <c r="U62" s="24" t="s">
         <v>51</v>
       </c>
@@ -5012,8 +5020,8 @@
     <mergeCell ref="U4:U5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="14" scale="53" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="24" max="80" man="1"/>
   </colBreaks>
@@ -5060,21 +5068,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -5086,17 +5094,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -5116,13 +5124,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -5162,10 +5170,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -5173,9 +5181,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -7872,17 +7880,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -8191,21 +8199,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -8217,17 +8225,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -8247,13 +8255,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -8293,10 +8301,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -8304,9 +8312,9 @@
       <c r="Q5" s="105"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -11001,17 +11009,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -11320,21 +11328,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -11346,17 +11354,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -11376,13 +11384,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -11422,10 +11430,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -11433,9 +11441,9 @@
       <c r="Q5" s="106"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -14124,17 +14132,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -14443,21 +14451,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -14469,17 +14477,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -14499,13 +14507,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -14545,10 +14553,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -14556,9 +14564,9 @@
       <c r="Q5" s="107"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -17045,17 +17053,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -17364,21 +17372,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -17390,17 +17398,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -17420,13 +17428,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -17466,10 +17474,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -17477,9 +17485,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -20168,17 +20176,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -20487,21 +20495,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -20513,17 +20521,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -20543,13 +20551,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -20589,10 +20597,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -20600,9 +20608,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -23278,17 +23286,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -23597,21 +23605,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -23623,17 +23631,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -23653,13 +23661,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -23699,10 +23707,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -23710,9 +23718,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -26385,17 +26393,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -26704,21 +26712,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -26730,17 +26738,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -26760,13 +26768,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -26806,10 +26814,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -26817,9 +26825,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -29502,17 +29510,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -29821,21 +29829,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -29847,17 +29855,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -29877,13 +29885,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -29923,10 +29931,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -29934,9 +29942,9 @@
       <c r="Q5" s="109"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -32601,17 +32609,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -32920,21 +32928,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -32946,17 +32954,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -32976,13 +32984,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -33022,10 +33030,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -33033,9 +33041,9 @@
       <c r="Q5" s="110"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -35693,17 +35701,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -36012,21 +36020,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -36038,17 +36046,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -36068,13 +36076,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -36114,10 +36122,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -36125,9 +36133,9 @@
       <c r="Q5" s="94"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -38815,17 +38823,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -39134,21 +39142,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -39160,17 +39168,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -39190,13 +39198,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -39236,10 +39244,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -39247,9 +39255,9 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -39326,34 +39334,48 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>38</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
       <c r="M7" s="57"/>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>1</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>41.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -39388,7 +39410,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>9+15+63</f>
+        <v>87</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -39411,11 +39436,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -39450,7 +39475,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>5</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -39473,11 +39500,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -39579,10 +39606,14 @@
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -39593,15 +39624,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -39634,7 +39665,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>720+72+576+60+63+432+18+1440</f>
+        <v>3381</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -39644,24 +39678,32 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
+      <c r="M12" s="64">
+        <v>22</v>
+      </c>
+      <c r="N12" s="65">
+        <v>15</v>
+      </c>
+      <c r="O12" s="66">
+        <v>8</v>
+      </c>
+      <c r="P12" s="67">
+        <v>18</v>
+      </c>
       <c r="Q12" s="67"/>
       <c r="R12" s="68"/>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>81897</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3412.375</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -39703,12 +39745,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>2</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="H13" s="71">
+        <v>16</v>
+      </c>
       <c r="I13" s="71"/>
       <c r="J13" s="72"/>
       <c r="K13" s="73"/>
@@ -39722,15 +39768,15 @@
       <c r="S13" s="56"/>
       <c r="T13" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -39947,7 +39993,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>2</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -39957,7 +40005,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -39970,11 +40020,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -40068,12 +40118,16 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>2</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="H19" s="71">
+        <v>20</v>
+      </c>
       <c r="I19" s="71"/>
       <c r="J19" s="72"/>
       <c r="K19" s="73"/>
@@ -40087,15 +40141,15 @@
       <c r="S19" s="56"/>
       <c r="T19" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -40129,12 +40183,16 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>5</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
       <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="H20" s="71">
+        <v>16</v>
+      </c>
       <c r="I20" s="71"/>
       <c r="J20" s="72"/>
       <c r="K20" s="73"/>
@@ -40148,15 +40206,15 @@
       <c r="S20" s="56"/>
       <c r="T20" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -40190,7 +40248,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>2</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -40200,7 +40260,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -40213,11 +40275,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -40256,7 +40318,9 @@
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
       <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="H22" s="71">
+        <v>20</v>
+      </c>
       <c r="I22" s="71"/>
       <c r="J22" s="72"/>
       <c r="K22" s="73"/>
@@ -40270,15 +40334,15 @@
       <c r="S22" s="56"/>
       <c r="T22" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -40321,7 +40385,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>35</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -40333,22 +40399,28 @@
       <c r="L23" s="56"/>
       <c r="M23" s="74"/>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>1</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>2</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -40391,7 +40463,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>6</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -40414,11 +40488,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -40452,34 +40526,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <v>40</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>1</v>
+      </c>
       <c r="N25" s="75"/>
-      <c r="O25" s="71"/>
+      <c r="O25" s="71">
+        <v>1</v>
+      </c>
       <c r="P25" s="72"/>
       <c r="Q25" s="72"/>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>42.458333333333336</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -40494,7 +40578,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>7</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -40517,11 +40603,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -40579,7 +40665,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <v>55</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -40591,9 +40679,13 @@
       <c r="L28" s="56"/>
       <c r="M28" s="74"/>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
+      <c r="O28" s="71">
+        <v>3</v>
+      </c>
       <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="Q28" s="72">
+        <v>3</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
@@ -40602,11 +40694,11 @@
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -40664,7 +40756,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>43</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -40687,11 +40781,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -40816,34 +40910,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>57+4</f>
+        <v>61</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>10</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1805</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>75.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40930,7 +41037,10 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>972+53+1512</f>
+        <v>2537</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
@@ -40938,26 +41048,32 @@
       <c r="H37" s="60"/>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>2</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>8</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>30</v>
+      </c>
       <c r="P37" s="67"/>
       <c r="Q37" s="67"/>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>15452</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>2575.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -40969,7 +41085,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>8</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -40992,11 +41110,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -41017,16 +41135,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -41036,34 +41154,43 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>21+378</f>
+        <v>399</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
       <c r="Q40" s="67"/>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>9624</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -41074,34 +41201,45 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>1056+1</f>
+        <v>1057</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>40</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>5</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>20</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>13473</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1122.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -41141,34 +41279,51 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5400+5940+7560+1836+4536+6480+73</f>
+        <v>31825</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
       <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>13*6+4</f>
+        <v>82</v>
+      </c>
+      <c r="K43" s="68">
+        <f>21*6+2</f>
+        <v>128</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>433</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>256</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>65</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>195691</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>32615.166666666668</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -41284,34 +41439,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>2268+29</f>
+        <v>2297</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
       <c r="G47" s="66"/>
-      <c r="H47" s="66"/>
+      <c r="H47" s="66">
+        <v>2</v>
+      </c>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>4</v>
+      </c>
       <c r="L47" s="63"/>
       <c r="M47" s="64"/>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>13870</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2311.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -41322,7 +41490,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -41345,11 +41515,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -41436,7 +41606,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -41459,11 +41631,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -41512,7 +41684,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -41535,11 +41709,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -41665,7 +41839,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>41934</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -41679,39 +41853,39 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
@@ -41720,15 +41894,15 @@
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>447</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>340779</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>42912.625</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -41736,17 +41910,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -41998,13 +42172,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -42055,21 +42229,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -42081,17 +42255,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -42111,13 +42285,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -42157,10 +42331,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -42168,9 +42342,9 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -42247,34 +42421,50 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>34</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>2</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>2</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>3</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>41.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -42309,7 +42499,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>8+63+15</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -42323,7 +42516,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>1</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -42332,11 +42527,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -42371,7 +42566,9 @@
       <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="71">
+        <v>1</v>
+      </c>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
@@ -42385,7 +42582,9 @@
       <c r="N9" s="75"/>
       <c r="O9" s="71"/>
       <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
+      <c r="Q9" s="72">
+        <v>2</v>
+      </c>
       <c r="R9" s="73"/>
       <c r="S9" s="56"/>
       <c r="T9" s="76">
@@ -42394,11 +42593,11 @@
       </c>
       <c r="U9" s="77">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V9" s="77">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W9" s="50"/>
       <c r="AF9" s="12"/>
@@ -42500,10 +42699,14 @@
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -42514,15 +42717,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -42555,7 +42758,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>72+720+63+43+360+64+1440+576</f>
+        <v>3338</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -42565,24 +42771,34 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
+      <c r="M12" s="64">
+        <v>14</v>
+      </c>
+      <c r="N12" s="65">
+        <v>10</v>
+      </c>
+      <c r="O12" s="66">
+        <v>10</v>
+      </c>
+      <c r="P12" s="67">
+        <v>22</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>25</v>
+      </c>
       <c r="R12" s="68"/>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>81320</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3388.3333333333335</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -42624,12 +42840,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>2</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="H13" s="71">
+        <v>16</v>
+      </c>
       <c r="I13" s="71"/>
       <c r="J13" s="72"/>
       <c r="K13" s="73"/>
@@ -42643,15 +42863,15 @@
       <c r="S13" s="56"/>
       <c r="T13" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -42868,7 +43088,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>2</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -42878,7 +43100,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -42891,11 +43115,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -42989,12 +43213,16 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>2</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="H19" s="71">
+        <v>20</v>
+      </c>
       <c r="I19" s="71"/>
       <c r="J19" s="72"/>
       <c r="K19" s="73"/>
@@ -43008,15 +43236,15 @@
       <c r="S19" s="56"/>
       <c r="T19" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -43050,12 +43278,16 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>5</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
       <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="H20" s="71">
+        <v>16</v>
+      </c>
       <c r="I20" s="71"/>
       <c r="J20" s="72"/>
       <c r="K20" s="73"/>
@@ -43069,15 +43301,15 @@
       <c r="S20" s="56"/>
       <c r="T20" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -43111,7 +43343,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>2</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -43121,7 +43355,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -43134,11 +43370,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -43177,7 +43413,9 @@
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
       <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="H22" s="71">
+        <v>20</v>
+      </c>
       <c r="I22" s="71"/>
       <c r="J22" s="72"/>
       <c r="K22" s="73"/>
@@ -43191,15 +43429,15 @@
       <c r="S22" s="56"/>
       <c r="T22" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -43242,7 +43480,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>34</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -43252,24 +43492,32 @@
       <c r="J23" s="72"/>
       <c r="K23" s="73"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="74"/>
+      <c r="M23" s="74">
+        <v>1</v>
+      </c>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>1</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>2</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -43312,7 +43560,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>6</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -43335,11 +43585,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -43373,34 +43623,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <v>40</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>1</v>
+      </c>
       <c r="N25" s="75"/>
       <c r="O25" s="71"/>
-      <c r="P25" s="72"/>
+      <c r="P25" s="72">
+        <v>12</v>
+      </c>
       <c r="Q25" s="72"/>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>41.958333333333336</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -43415,7 +43675,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>7</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -43438,11 +43700,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -43500,7 +43762,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <v>51</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -43510,24 +43774,32 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>2</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="O28" s="71">
+        <v>1</v>
+      </c>
+      <c r="P28" s="72">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="72">
+        <v>3</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -43585,7 +43857,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>43</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -43608,11 +43882,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -43737,34 +44011,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>57+1</f>
+        <v>58</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>2</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>2</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1541</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -43851,7 +44138,10 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>864+1512</f>
+        <v>2376</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
@@ -43859,26 +44149,34 @@
       <c r="H37" s="60"/>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>2</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>36</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>30</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>108</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>15302</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>2550.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -43890,7 +44188,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>8</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -43913,11 +44213,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -43938,16 +44238,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
-      <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="73"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -43957,34 +44257,45 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>378+19</f>
+        <v>397</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>9624</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -43995,34 +44306,45 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>80+1+960</f>
+        <v>1041</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>10</v>
+      </c>
       <c r="N41" s="90"/>
-      <c r="O41" s="85"/>
+      <c r="O41" s="85">
+        <v>7</v>
+      </c>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>20</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>12945</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1078.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -44062,34 +44384,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5400+5940+6480+1728+4536+6480+1836</f>
+        <v>32400</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="66">
+        <v>2</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>14*6+2</f>
+        <v>86</v>
+      </c>
+      <c r="K43" s="68">
+        <f>21*6+2</f>
+        <v>128</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>277</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>380</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>542</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>201817</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>33636.166666666664</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -44205,34 +44546,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>2268+29</f>
+        <v>2297</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
       <c r="G47" s="66"/>
-      <c r="H47" s="66"/>
+      <c r="H47" s="66">
+        <v>2</v>
+      </c>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>4</v>
+      </c>
       <c r="L47" s="63"/>
       <c r="M47" s="64"/>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>13870</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2311.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -44243,7 +44597,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -44266,11 +44622,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -44357,7 +44713,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -44380,11 +44738,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -44433,7 +44791,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -44456,11 +44816,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -44586,7 +44946,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>42270</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -44600,39 +44960,39 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>437</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
@@ -44641,15 +45001,15 @@
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>476</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>345242</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>43823.583333333328</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -44657,17 +45017,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -44919,13 +45279,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -44976,21 +45336,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -45002,17 +45362,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -45032,13 +45392,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -45078,10 +45438,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -45089,9 +45449,9 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -47578,17 +47938,2938 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
+      <c r="U60" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="45"/>
+      <c r="K61" s="20"/>
+      <c r="U61" s="7"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="44"/>
+      <c r="K62" s="21"/>
+      <c r="U62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="23"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="20"/>
+      <c r="U65" s="7"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="44"/>
+      <c r="K66" s="21"/>
+      <c r="U66" s="3"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="46"/>
+      <c r="K67" s="23"/>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="20"/>
+      <c r="U69" s="7"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="44"/>
+      <c r="K70" s="21"/>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="23"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="20"/>
+      <c r="U73" s="7"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="44"/>
+      <c r="K74" s="21"/>
+      <c r="U74" s="3"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="46"/>
+      <c r="K75" s="23"/>
+      <c r="U75" s="8"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="20"/>
+      <c r="U77" s="7"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="21"/>
+      <c r="U78" s="3"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="23"/>
+      <c r="U79" s="8"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="18"/>
+      <c r="U81" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE32B2FB-9696-404D-A440-813A4AD11A51}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="28" customWidth="1"/>
+    <col min="3" max="6" width="10" style="9" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="9" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="10" style="9" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="9" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="9" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="9" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="9" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="120" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="121" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
+      <c r="M4" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="S4" s="9"/>
+      <c r="T4" s="124" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="130" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="113" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="11"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="11"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="11"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="11"/>
+      <c r="AT4" s="11"/>
+      <c r="AU4" s="11"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="11"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="11"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="11"/>
+      <c r="BB4" s="11"/>
+    </row>
+    <row r="5" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="37"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="128" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" s="129"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="11"/>
+      <c r="AT5" s="11"/>
+      <c r="AU5" s="11"/>
+      <c r="AV5" s="11"/>
+      <c r="AW5" s="11"/>
+      <c r="AX5" s="11"/>
+      <c r="AY5" s="11"/>
+      <c r="AZ5" s="11"/>
+      <c r="BA5" s="11"/>
+      <c r="BB5" s="11"/>
+    </row>
+    <row r="6" spans="1:54" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="38"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="112"/>
+      <c r="Q6" s="112"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="11"/>
+      <c r="AM6" s="11"/>
+      <c r="AN6" s="11"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AR6" s="11"/>
+      <c r="AS6" s="11"/>
+      <c r="AT6" s="11"/>
+      <c r="AU6" s="11"/>
+      <c r="AV6" s="11"/>
+      <c r="AW6" s="11"/>
+      <c r="AX6" s="11"/>
+      <c r="AY6" s="11"/>
+      <c r="AZ6" s="11"/>
+      <c r="BA6" s="11"/>
+      <c r="BB6" s="11"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>1</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="53"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="59">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="59">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="59">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="50"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="12"/>
+      <c r="AP7" s="12"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="12"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="12"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="12"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="12"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="12"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="69">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="70">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="70">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="50"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="77">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="77">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="50"/>
+      <c r="AF9" s="12"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="12"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="50"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="72"/>
+      <c r="Q11" s="72"/>
+      <c r="R11" s="73"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="12"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+    </row>
+    <row r="12" spans="1:54" s="13" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>7</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="70">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="70">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="12"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="12"/>
+      <c r="AI12" s="12"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="27">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="74"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="72"/>
+      <c r="Q13" s="72"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="77">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="77">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="12"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="27">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="74"/>
+      <c r="N14" s="75"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="76">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="76">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="12"/>
+      <c r="AI15" s="12"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="74"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="12"/>
+      <c r="AI17" s="12"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="27">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="74"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="12"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="74"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="12"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="12"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+    </row>
+    <row r="22" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="27">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="75"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="12"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="12"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+    </row>
+    <row r="23" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="27">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="74"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="27">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="74"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="14" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+    </row>
+    <row r="27" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+    </row>
+    <row r="28" spans="1:54" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="72"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="76">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="62"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="68"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="78">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="78">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="50"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="72"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="73"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="76">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="76">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="76">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="66"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="68"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="78">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="78">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="78">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="85"/>
+      <c r="F41" s="85"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="85"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="89"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="85"/>
+      <c r="P41" s="86"/>
+      <c r="Q41" s="86"/>
+      <c r="R41" s="87"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="91">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="91">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="71"/>
+      <c r="G42" s="71"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="75"/>
+      <c r="O42" s="71"/>
+      <c r="P42" s="72"/>
+      <c r="Q42" s="72"/>
+      <c r="R42" s="73"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="76"/>
+      <c r="U42" s="76"/>
+      <c r="V42" s="76"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="63"/>
+      <c r="M43" s="64"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="66"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="68"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="78">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="78">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="78">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="75"/>
+      <c r="O44" s="71"/>
+      <c r="P44" s="72"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="73"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="76"/>
+      <c r="U44" s="76"/>
+      <c r="V44" s="76"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="72"/>
+      <c r="K45" s="73"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="74"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="71"/>
+      <c r="P45" s="72"/>
+      <c r="Q45" s="72"/>
+      <c r="R45" s="73"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="76">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="76">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="76">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="74"/>
+      <c r="N46" s="75"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="76">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="76">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="67"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="63"/>
+      <c r="M47" s="64"/>
+      <c r="N47" s="65"/>
+      <c r="O47" s="66"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="78">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="78">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="71"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="71"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="74"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="71"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="72"/>
+      <c r="K50" s="73"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="74"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="71"/>
+      <c r="P50" s="72"/>
+      <c r="Q50" s="72"/>
+      <c r="R50" s="73"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="76">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="27">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="64"/>
+      <c r="N51" s="65"/>
+      <c r="O51" s="66"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="78">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="78">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="72"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="74"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="71"/>
+      <c r="P52" s="72"/>
+      <c r="Q52" s="72"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="76">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="74"/>
+      <c r="N53" s="75"/>
+      <c r="O53" s="71"/>
+      <c r="P53" s="72"/>
+      <c r="Q53" s="72"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="26"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="72"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="74"/>
+      <c r="N54" s="75"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="72"/>
+      <c r="Q54" s="72"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="76">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="76">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="76">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="26"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="71"/>
+      <c r="G55" s="71"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="72"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="74"/>
+      <c r="N55" s="75"/>
+      <c r="O55" s="71"/>
+      <c r="P55" s="72"/>
+      <c r="Q55" s="72"/>
+      <c r="R55" s="73"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="76"/>
+      <c r="U55" s="76"/>
+      <c r="V55" s="76"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="26"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="71"/>
+      <c r="G56" s="71"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="73"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="74"/>
+      <c r="N56" s="75"/>
+      <c r="O56" s="71"/>
+      <c r="P56" s="72"/>
+      <c r="Q56" s="72"/>
+      <c r="R56" s="73"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="76"/>
+      <c r="U56" s="76"/>
+      <c r="V56" s="76"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="71"/>
+      <c r="F57" s="71"/>
+      <c r="G57" s="71"/>
+      <c r="H57" s="71"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="73"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="74"/>
+      <c r="N57" s="75"/>
+      <c r="O57" s="71"/>
+      <c r="P57" s="72"/>
+      <c r="Q57" s="72"/>
+      <c r="R57" s="73"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+    </row>
+    <row r="58" spans="1:22" s="15" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="2">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="5">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="56"/>
+      <c r="T58" s="4">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -47897,21 +51178,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -47923,17 +51204,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -47953,13 +51234,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -47999,10 +51280,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -48010,9 +51291,9 @@
       <c r="Q5" s="52"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -50700,17 +53981,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -51019,21 +54300,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -51045,17 +54326,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -51075,13 +54356,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -51121,10 +54402,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -51132,9 +54413,9 @@
       <c r="Q5" s="98"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -53810,17 +57091,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -54129,21 +57410,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -54155,17 +57436,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -54185,13 +57466,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="125" t="s">
+      <c r="U4" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -54231,10 +57512,10 @@
       <c r="I5" s="101" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="115"/>
+      <c r="K5" s="116"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -54242,9 +57523,9 @@
       <c r="Q5" s="92"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -56910,17 +60191,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -57229,21 +60510,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -57255,17 +60536,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -57285,13 +60566,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -57331,10 +60612,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -57342,9 +60623,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -60025,17 +63306,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -60344,21 +63625,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -60370,17 +63651,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -60400,13 +63681,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -60446,10 +63727,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -60457,9 +63738,9 @@
       <c r="Q5" s="99"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -63137,17 +66418,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -63456,21 +66737,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -63482,17 +66763,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -63512,13 +66793,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -63558,10 +66839,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -63569,9 +66850,9 @@
       <c r="Q5" s="100"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -66259,17 +69540,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>
@@ -66578,21 +69859,21 @@
       <c r="B1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="119" t="s">
+      <c r="I1" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
@@ -66604,17 +69885,17 @@
       <c r="B4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="120" t="s">
+      <c r="C4" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="123"/>
       <c r="M4" s="34" t="s">
         <v>0</v>
       </c>
@@ -66634,13 +69915,13 @@
         <v>61</v>
       </c>
       <c r="S4" s="9"/>
-      <c r="T4" s="123" t="s">
+      <c r="T4" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="U4" s="129" t="s">
+      <c r="U4" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="V4" s="112" t="s">
+      <c r="V4" s="113" t="s">
         <v>66</v>
       </c>
       <c r="AF4" s="11"/>
@@ -66680,10 +69961,10 @@
       <c r="I5" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="127" t="s">
+      <c r="J5" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="128"/>
+      <c r="K5" s="129"/>
       <c r="M5" s="37"/>
       <c r="N5" s="49"/>
       <c r="O5" s="40"/>
@@ -66691,9 +69972,9 @@
       <c r="Q5" s="104"/>
       <c r="R5" s="38"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="124"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="113"/>
+      <c r="T5" s="125"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="114"/>
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
@@ -69396,17 +72677,17 @@
       <c r="B60" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C60" s="116" t="s">
+      <c r="C60" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117"/>
-      <c r="H60" s="117"/>
-      <c r="I60" s="117"/>
-      <c r="J60" s="117"/>
-      <c r="K60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="119"/>
       <c r="U60" s="24" t="s">
         <v>51</v>
       </c>

--- a/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
+++ b/GBDS MARCH FILES 2026/INVENTORY COUNT SHEET - MARCH 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MARCH FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD447EA1-1EDE-4071-BA99-865A3682E361}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF53247-ECC1-4966-B873-E546BA590EA6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="32" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <sheet name="03-25-2026" sheetId="48" r:id="rId19"/>
     <sheet name="03-26-2026" sheetId="49" r:id="rId20"/>
     <sheet name="03-27-2026" sheetId="50" r:id="rId21"/>
-    <sheet name="03-28-2026" sheetId="51" r:id="rId22"/>
+    <sheet name="03-30-2026" sheetId="51" r:id="rId22"/>
     <sheet name="03-29-2026" sheetId="52" r:id="rId23"/>
   </sheets>
   <definedNames>
@@ -58,8 +58,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="18">'03-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'03-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'03-27-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="21">'03-28-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'03-29-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'03-30-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$W$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -354,10 +354,10 @@
     <t>DATE: 03/27/2026</t>
   </si>
   <si>
-    <t>DATE: 03/28/2026</t>
+    <t>DATE: 03/29/2026</t>
   </si>
   <si>
-    <t>DATE: 03/29/2026</t>
+    <t>DATE: 03/30/2026</t>
   </si>
 </sst>
 </file>
@@ -45354,7 +45354,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -45528,34 +45528,50 @@
       <c r="B7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="53"/>
+      <c r="C7" s="53">
+        <v>34</v>
+      </c>
       <c r="D7" s="53"/>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
+      <c r="H7" s="53">
+        <v>2</v>
+      </c>
+      <c r="I7" s="53">
+        <v>1</v>
+      </c>
       <c r="J7" s="54"/>
-      <c r="K7" s="55"/>
+      <c r="K7" s="55">
+        <v>6</v>
+      </c>
       <c r="L7" s="56"/>
-      <c r="M7" s="57"/>
+      <c r="M7" s="57">
+        <v>2</v>
+      </c>
       <c r="N7" s="58"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
+      <c r="O7" s="53">
+        <v>1</v>
+      </c>
+      <c r="P7" s="54">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="54">
+        <v>3</v>
+      </c>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
       <c r="T7" s="59">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U7" s="59">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>981</v>
       </c>
       <c r="V7" s="59">
         <f>U7/24</f>
-        <v>0</v>
+        <v>40.875</v>
       </c>
       <c r="W7" s="50"/>
       <c r="AF7" s="12"/>
@@ -45590,7 +45606,10 @@
       <c r="B8" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="60">
+        <f>8+15+63</f>
+        <v>86</v>
+      </c>
       <c r="D8" s="60"/>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -45604,7 +45623,9 @@
       <c r="N8" s="65"/>
       <c r="O8" s="66"/>
       <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
+      <c r="Q8" s="67">
+        <v>1</v>
+      </c>
       <c r="R8" s="68"/>
       <c r="S8" s="63"/>
       <c r="T8" s="69">
@@ -45613,11 +45634,11 @@
       </c>
       <c r="U8" s="70">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2088</v>
       </c>
       <c r="V8" s="70">
         <f>U8/24</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="W8" s="50"/>
       <c r="AF8" s="12"/>
@@ -45781,10 +45802,14 @@
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
+      <c r="H11" s="71">
+        <v>22</v>
+      </c>
       <c r="I11" s="71"/>
       <c r="J11" s="72"/>
-      <c r="K11" s="73"/>
+      <c r="K11" s="73">
+        <v>2</v>
+      </c>
       <c r="L11" s="56"/>
       <c r="M11" s="74"/>
       <c r="N11" s="75"/>
@@ -45795,15 +45820,15 @@
       <c r="S11" s="56"/>
       <c r="T11" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="59">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
@@ -45836,7 +45861,10 @@
       <c r="B12" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="60">
+        <f>720+72+63+43+360+20+1440+576</f>
+        <v>3294</v>
+      </c>
       <c r="D12" s="60"/>
       <c r="E12" s="60"/>
       <c r="F12" s="60"/>
@@ -45846,24 +45874,34 @@
       <c r="J12" s="61"/>
       <c r="K12" s="62"/>
       <c r="L12" s="63"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="65"/>
+      <c r="M12" s="64">
+        <v>35</v>
+      </c>
+      <c r="N12" s="65">
+        <v>11</v>
+      </c>
       <c r="O12" s="66"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
+      <c r="P12" s="67">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>19</v>
+      </c>
+      <c r="R12" s="68">
+        <v>18</v>
+      </c>
       <c r="S12" s="63"/>
       <c r="T12" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="U12" s="70">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>80400</v>
       </c>
       <c r="V12" s="70">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3350</v>
       </c>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -45905,12 +45943,16 @@
       <c r="B13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="71">
+        <v>2</v>
+      </c>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
       <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
+      <c r="H13" s="71">
+        <v>16</v>
+      </c>
       <c r="I13" s="71"/>
       <c r="J13" s="72"/>
       <c r="K13" s="73"/>
@@ -45924,15 +45966,15 @@
       <c r="S13" s="56"/>
       <c r="T13" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U13" s="77">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V13" s="77">
         <f>U13/24</f>
-        <v>0</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
@@ -46149,7 +46191,9 @@
       <c r="B17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="71">
+        <v>2</v>
+      </c>
       <c r="D17" s="71"/>
       <c r="E17" s="71"/>
       <c r="F17" s="71"/>
@@ -46159,7 +46203,9 @@
       <c r="J17" s="72"/>
       <c r="K17" s="73"/>
       <c r="L17" s="56"/>
-      <c r="M17" s="74"/>
+      <c r="M17" s="74">
+        <v>1</v>
+      </c>
       <c r="N17" s="75"/>
       <c r="O17" s="71"/>
       <c r="P17" s="72"/>
@@ -46172,11 +46218,11 @@
       </c>
       <c r="U17" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V17" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
@@ -46270,12 +46316,16 @@
       <c r="B19" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="71">
+        <v>2</v>
+      </c>
       <c r="D19" s="71"/>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
+      <c r="H19" s="71">
+        <v>20</v>
+      </c>
       <c r="I19" s="71"/>
       <c r="J19" s="72"/>
       <c r="K19" s="73"/>
@@ -46289,15 +46339,15 @@
       <c r="S19" s="56"/>
       <c r="T19" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U19" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="V19" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
@@ -46331,12 +46381,16 @@
       <c r="B20" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="71">
+        <v>5</v>
+      </c>
       <c r="D20" s="71"/>
       <c r="E20" s="71"/>
       <c r="F20" s="71"/>
       <c r="G20" s="71"/>
-      <c r="H20" s="71"/>
+      <c r="H20" s="71">
+        <v>16</v>
+      </c>
       <c r="I20" s="71"/>
       <c r="J20" s="72"/>
       <c r="K20" s="73"/>
@@ -46350,15 +46404,15 @@
       <c r="S20" s="56"/>
       <c r="T20" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U20" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="V20" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
@@ -46392,7 +46446,9 @@
       <c r="B21" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71"/>
+      <c r="C21" s="71">
+        <v>2</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
       <c r="F21" s="71"/>
@@ -46402,7 +46458,9 @@
       <c r="J21" s="72"/>
       <c r="K21" s="73"/>
       <c r="L21" s="56"/>
-      <c r="M21" s="74"/>
+      <c r="M21" s="74">
+        <v>1</v>
+      </c>
       <c r="N21" s="75"/>
       <c r="O21" s="71"/>
       <c r="P21" s="72"/>
@@ -46415,11 +46473,11 @@
       </c>
       <c r="U21" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V21" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
@@ -46458,7 +46516,9 @@
       <c r="E22" s="71"/>
       <c r="F22" s="71"/>
       <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
+      <c r="H22" s="71">
+        <v>20</v>
+      </c>
       <c r="I22" s="71"/>
       <c r="J22" s="72"/>
       <c r="K22" s="73"/>
@@ -46472,15 +46532,15 @@
       <c r="S22" s="56"/>
       <c r="T22" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U22" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V22" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -46523,7 +46583,9 @@
       <c r="B23" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="71"/>
+      <c r="C23" s="71">
+        <v>34</v>
+      </c>
       <c r="D23" s="71"/>
       <c r="E23" s="71"/>
       <c r="F23" s="71"/>
@@ -46535,22 +46597,28 @@
       <c r="L23" s="56"/>
       <c r="M23" s="74"/>
       <c r="N23" s="75"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
+      <c r="O23" s="71">
+        <v>1</v>
+      </c>
+      <c r="P23" s="72">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="72">
+        <v>2</v>
+      </c>
       <c r="R23" s="73"/>
       <c r="S23" s="56"/>
       <c r="T23" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="V23" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>37.791666666666664</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -46593,7 +46661,9 @@
       <c r="B24" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="71"/>
+      <c r="C24" s="71">
+        <v>6</v>
+      </c>
       <c r="D24" s="71"/>
       <c r="E24" s="71"/>
       <c r="F24" s="71"/>
@@ -46616,11 +46686,11 @@
       </c>
       <c r="U24" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V24" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
@@ -46654,34 +46724,44 @@
       <c r="B25" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="71">
+        <v>40</v>
+      </c>
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="71">
+        <v>10</v>
+      </c>
+      <c r="I25" s="71">
+        <v>1</v>
+      </c>
       <c r="J25" s="72"/>
       <c r="K25" s="73"/>
       <c r="L25" s="56"/>
-      <c r="M25" s="74"/>
+      <c r="M25" s="74">
+        <v>1</v>
+      </c>
       <c r="N25" s="75"/>
       <c r="O25" s="71"/>
-      <c r="P25" s="72"/>
+      <c r="P25" s="72">
+        <v>12</v>
+      </c>
       <c r="Q25" s="72"/>
       <c r="R25" s="73"/>
       <c r="S25" s="56"/>
       <c r="T25" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U25" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1007</v>
       </c>
       <c r="V25" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>41.958333333333336</v>
       </c>
       <c r="AY25" s="14" t="e">
         <f>#REF!-AY24</f>
@@ -46696,7 +46776,9 @@
       <c r="B26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="71"/>
+      <c r="C26" s="71">
+        <v>7</v>
+      </c>
       <c r="D26" s="71"/>
       <c r="E26" s="71"/>
       <c r="F26" s="71"/>
@@ -46719,11 +46801,11 @@
       </c>
       <c r="U26" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V26" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -46781,7 +46863,9 @@
       <c r="B28" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="71"/>
+      <c r="C28" s="71">
+        <v>47</v>
+      </c>
       <c r="D28" s="71"/>
       <c r="E28" s="71"/>
       <c r="F28" s="71"/>
@@ -46791,24 +46875,32 @@
       <c r="J28" s="72"/>
       <c r="K28" s="73"/>
       <c r="L28" s="56"/>
-      <c r="M28" s="74"/>
+      <c r="M28" s="74">
+        <v>1</v>
+      </c>
       <c r="N28" s="75"/>
-      <c r="O28" s="71"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
+      <c r="O28" s="71">
+        <v>1</v>
+      </c>
+      <c r="P28" s="72">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="72">
+        <v>4</v>
+      </c>
       <c r="R28" s="73"/>
       <c r="S28" s="56"/>
       <c r="T28" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U28" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="V28" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>53.5</v>
       </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -46866,7 +46958,9 @@
       <c r="B30" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="71"/>
+      <c r="C30" s="71">
+        <v>42</v>
+      </c>
       <c r="D30" s="71"/>
       <c r="E30" s="71"/>
       <c r="F30" s="71"/>
@@ -46880,7 +46974,9 @@
       <c r="N30" s="75"/>
       <c r="O30" s="71"/>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>1</v>
+      </c>
       <c r="R30" s="73"/>
       <c r="S30" s="56"/>
       <c r="T30" s="59">
@@ -46889,11 +46985,11 @@
       </c>
       <c r="U30" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="V30" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -47018,34 +47114,47 @@
       <c r="B34" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="71"/>
+      <c r="C34" s="71">
+        <f>57+72+1</f>
+        <v>130</v>
+      </c>
       <c r="D34" s="71"/>
       <c r="E34" s="71"/>
       <c r="F34" s="71"/>
       <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
+      <c r="H34" s="71">
+        <v>4</v>
+      </c>
       <c r="I34" s="71"/>
       <c r="J34" s="72"/>
-      <c r="K34" s="73"/>
+      <c r="K34" s="73">
+        <v>1</v>
+      </c>
       <c r="L34" s="56"/>
-      <c r="M34" s="74"/>
+      <c r="M34" s="74">
+        <v>2</v>
+      </c>
       <c r="N34" s="75"/>
-      <c r="O34" s="71"/>
+      <c r="O34" s="71">
+        <v>2</v>
+      </c>
       <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
+      <c r="Q34" s="72">
+        <v>1</v>
+      </c>
       <c r="R34" s="73"/>
       <c r="S34" s="56"/>
       <c r="T34" s="59">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U34" s="76">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3245</v>
       </c>
       <c r="V34" s="76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>135.20833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47132,7 +47241,10 @@
       <c r="B37" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="60">
+        <f>648+88+1296+1512</f>
+        <v>3544</v>
+      </c>
       <c r="D37" s="60"/>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
@@ -47140,26 +47252,34 @@
       <c r="H37" s="60"/>
       <c r="I37" s="60"/>
       <c r="J37" s="61"/>
-      <c r="K37" s="62"/>
+      <c r="K37" s="62">
+        <v>2</v>
+      </c>
       <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
+      <c r="M37" s="64">
+        <v>11</v>
+      </c>
       <c r="N37" s="65"/>
-      <c r="O37" s="66"/>
+      <c r="O37" s="66">
+        <v>5</v>
+      </c>
       <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
+      <c r="Q37" s="67">
+        <v>116</v>
+      </c>
       <c r="R37" s="68"/>
       <c r="S37" s="63"/>
       <c r="T37" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" s="78">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>22058</v>
       </c>
       <c r="V37" s="78">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3676.3333333333335</v>
       </c>
       <c r="W37" s="50"/>
     </row>
@@ -47171,7 +47291,9 @@
       <c r="B38" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="71"/>
+      <c r="C38" s="71">
+        <v>8</v>
+      </c>
       <c r="D38" s="71"/>
       <c r="E38" s="71"/>
       <c r="F38" s="71"/>
@@ -47194,11 +47316,11 @@
       </c>
       <c r="U38" s="76">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V38" s="76">
         <f>U38/24</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -47219,16 +47341,16 @@
       <c r="J39" s="80"/>
       <c r="K39" s="81"/>
       <c r="L39" s="56"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="81"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="53"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="55"/>
       <c r="S39" s="56"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
+      <c r="T39" s="59"/>
+      <c r="U39" s="59"/>
+      <c r="V39" s="59"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
@@ -47238,34 +47360,45 @@
       <c r="B40" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="60">
+        <f>19+378</f>
+        <v>397</v>
+      </c>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
       <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
+      <c r="H40" s="60">
+        <v>4</v>
+      </c>
       <c r="I40" s="60"/>
       <c r="J40" s="61"/>
-      <c r="K40" s="62"/>
+      <c r="K40" s="62">
+        <v>20</v>
+      </c>
       <c r="L40" s="63"/>
       <c r="M40" s="64"/>
       <c r="N40" s="65"/>
-      <c r="O40" s="66"/>
+      <c r="O40" s="66">
+        <v>1</v>
+      </c>
       <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
+      <c r="Q40" s="67">
+        <v>2</v>
+      </c>
       <c r="R40" s="68"/>
       <c r="S40" s="63"/>
       <c r="T40" s="78">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U40" s="78">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>9624</v>
       </c>
       <c r="V40" s="78">
         <f>U40/24</f>
-        <v>0</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -47276,34 +47409,43 @@
       <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="85"/>
+      <c r="C41" s="85">
+        <f>192+960+42</f>
+        <v>1194</v>
+      </c>
       <c r="D41" s="85"/>
       <c r="E41" s="85"/>
       <c r="F41" s="85"/>
       <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
+      <c r="H41" s="85">
+        <v>9</v>
+      </c>
       <c r="I41" s="85"/>
       <c r="J41" s="86"/>
       <c r="K41" s="87"/>
       <c r="L41" s="88"/>
-      <c r="M41" s="89"/>
+      <c r="M41" s="89">
+        <v>24</v>
+      </c>
       <c r="N41" s="90"/>
       <c r="O41" s="85"/>
       <c r="P41" s="86"/>
-      <c r="Q41" s="86"/>
+      <c r="Q41" s="86">
+        <v>20</v>
+      </c>
       <c r="R41" s="87"/>
       <c r="S41" s="88"/>
       <c r="T41" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U41" s="91">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>14865</v>
       </c>
       <c r="V41" s="91">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1238.75</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47343,34 +47485,53 @@
       <c r="B43" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="66"/>
+      <c r="C43" s="66">
+        <f>5400+5940+5184+5616+4536+6480</f>
+        <v>33156</v>
+      </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
       <c r="F43" s="66"/>
       <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="67"/>
-      <c r="K43" s="68"/>
+      <c r="H43" s="66">
+        <v>5</v>
+      </c>
+      <c r="I43" s="66">
+        <v>7</v>
+      </c>
+      <c r="J43" s="67">
+        <f>15*6+4</f>
+        <v>94</v>
+      </c>
+      <c r="K43" s="68">
+        <f>21*6+2</f>
+        <v>128</v>
+      </c>
       <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
+      <c r="M43" s="64">
+        <v>677</v>
+      </c>
       <c r="N43" s="65"/>
-      <c r="O43" s="66"/>
+      <c r="O43" s="66">
+        <v>50</v>
+      </c>
       <c r="P43" s="67"/>
-      <c r="Q43" s="67"/>
+      <c r="Q43" s="67">
+        <v>541</v>
+      </c>
       <c r="R43" s="68"/>
       <c r="S43" s="63"/>
       <c r="T43" s="78">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="U43" s="78">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>206778</v>
       </c>
       <c r="V43" s="78">
         <f>U43/6</f>
-        <v>0</v>
+        <v>34463</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47486,34 +47647,47 @@
       <c r="B47" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="66"/>
+      <c r="C47" s="66">
+        <f>2268+29</f>
+        <v>2297</v>
+      </c>
       <c r="D47" s="66"/>
       <c r="E47" s="66"/>
       <c r="F47" s="66"/>
       <c r="G47" s="66"/>
-      <c r="H47" s="66"/>
+      <c r="H47" s="66">
+        <v>2</v>
+      </c>
       <c r="I47" s="66"/>
       <c r="J47" s="67"/>
-      <c r="K47" s="68"/>
+      <c r="K47" s="68">
+        <v>4</v>
+      </c>
       <c r="L47" s="63"/>
       <c r="M47" s="64"/>
       <c r="N47" s="65"/>
-      <c r="O47" s="66"/>
-      <c r="P47" s="67"/>
-      <c r="Q47" s="67"/>
+      <c r="O47" s="66">
+        <v>3</v>
+      </c>
+      <c r="P47" s="67">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="67">
+        <v>10</v>
+      </c>
       <c r="R47" s="68"/>
       <c r="S47" s="63"/>
       <c r="T47" s="78">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="78">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>13870</v>
       </c>
       <c r="V47" s="78">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2311.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -47524,7 +47698,9 @@
       <c r="B48" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="71"/>
+      <c r="C48" s="71">
+        <v>1</v>
+      </c>
       <c r="D48" s="71"/>
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
@@ -47547,11 +47723,11 @@
       </c>
       <c r="U48" s="76">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V48" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -47638,7 +47814,9 @@
       <c r="B51" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C51" s="66"/>
+      <c r="C51" s="66">
+        <v>34</v>
+      </c>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
@@ -47661,11 +47839,11 @@
       </c>
       <c r="U51" s="78">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="78">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -47714,7 +47892,9 @@
       <c r="B53" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C53" s="71"/>
+      <c r="C53" s="71">
+        <v>5</v>
+      </c>
       <c r="D53" s="71"/>
       <c r="E53" s="71"/>
       <c r="F53" s="71"/>
@@ -47737,11 +47917,11 @@
       </c>
       <c r="U53" s="76">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V53" s="76">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -47867,7 +48047,7 @@
       </c>
       <c r="C58" s="2">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>44369</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -47881,56 +48061,56 @@
       </c>
       <c r="H58" s="2">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="K58" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M58" s="5">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="N58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="Q58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="R58" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S58" s="56"/>
       <c r="T58" s="4">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
+        <v>503</v>
+      </c>
+      <c r="U58" s="95">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>359447</v>
       </c>
       <c r="V58" s="4">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>45960.083333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -48275,7 +48455,7 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -51121,13 +51301,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
